--- a/docs/downloads/Belleville.xlsx
+++ b/docs/downloads/Belleville.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D376"/>
+  <dimension ref="A1:D440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Daphne</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wachner</t>
+          <t>Chang</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>awachnerextra@gmail.com</t>
+          <t>hwah0902@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Wachner</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kevintaylor506@hotmail.com</t>
+          <t>awachnerextra@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>johnkrussell10@gmail.com</t>
+          <t>kevintaylor506@hotmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kory</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Moxam</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>korymoxam11299@gmail.com</t>
+          <t>johnkrussell10@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Kory</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>De jeuses-gautier</t>
+          <t>Moxam</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kathleendejeuses@yahoo.com</t>
+          <t>korymoxam11299@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kukkonen</t>
+          <t>De jeuses-gautier</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>beth.kukkonen@gmail.com</t>
+          <t>kathleendejeuses@yahoo.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alwell</t>
+          <t>Kukkonen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ken.alwell50@gmail.com</t>
+          <t>beth.kukkonen@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Adele</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tate</t>
+          <t>Alwell</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ruby.adele.tate@gmail.com</t>
+          <t>ken.alwell50@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Adele</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Tate</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>gk@gmail.com</t>
+          <t>ruby.adele.tate@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Barbeau</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jimbarbeau8@gmail.com</t>
+          <t>gk@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kalvin</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Holland</t>
+          <t>Barbeau</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kalvin.holland4@gmail.com</t>
+          <t>jimbarbeau8@gmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Kalvin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kapadiya</t>
+          <t>Holland</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rktemp@gmail.com</t>
+          <t>kalvin.holland4@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>De jong</t>
+          <t>Kapadiya</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jjdejong14@outlook.com</t>
+          <t>rktemp@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Markus</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Morin</t>
+          <t>De jong</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>markus.p.morin@gmail.com</t>
+          <t>jjdejong14@outlook.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Markus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Morin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kerryhill65@gmail.com</t>
+          <t>markus.p.morin@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Donald</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>donlinda2002@hotmail.com</t>
+          <t>kerryhill65@gmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Donald</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kerrwood@gmail.com</t>
+          <t>donlinda2002@hotmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Kerr</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abcdef$$@icloud.com</t>
+          <t>kerrwood@gmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lipan</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rlipan@hotmail.com</t>
+          <t>abcdef$$@icloud.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Miya</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hemmersbach</t>
+          <t>Lipan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>miya.hemmersbach@gmail.com</t>
+          <t>rlipan@hotmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Miya</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Reyburn</t>
+          <t>Hemmersbach</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jim@pickleplexclub.ca</t>
+          <t>miya.hemmersbach@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Boyce</t>
+          <t>Reyburn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>angela.trick@gmail.com</t>
+          <t>jim@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Moreton</t>
+          <t>Boyce</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>dropmeoff@hotmail.com</t>
+          <t>angela.trick@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Moreton</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>hggiguig@gmail.com</t>
+          <t>dropmeoff@hotmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>O'neil</t>
+          <t>Tai</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>doneil17@cogeco.ca</t>
+          <t>comtk0@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mckinnon</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ruth.m@safestart.com</t>
+          <t>hggiguig@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alistair</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Widling</t>
+          <t>O'neil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>dorianwidling@gmail.com</t>
+          <t>doneil17@cogeco.ca</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Mckinnon</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>catherineswarren@gmail.com</t>
+          <t>ruth.m@safestart.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Khushi</t>
+          <t>Alistair</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Prajapati</t>
+          <t>Widling</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kptest@gmail.com</t>
+          <t>dorianwidling@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>rileydavidson23@icloud.com</t>
+          <t>catherineswarren@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Khushi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Prajapati</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>timschaly58@gmail.com</t>
+          <t>kptest@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ludington</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jacobludington@icloud.com</t>
+          <t>rileydavidson23@icloud.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>belleville@pickleplexclub.ca</t>
+          <t>timschaly58@gmail.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Ludington</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>austinschaly1@gmail.com</t>
+          <t>jacobludington@icloud.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mayhew</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>steven62mayhew@gmail.com</t>
+          <t>belleville@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Delong</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>delongla36@gmail.com</t>
+          <t>austinschaly1@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Jeffery</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Coleman</t>
+          <t>Mayhew</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jeffery.coleman@gmail.com</t>
+          <t>steven62mayhew@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Delong</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>mzjonesey@gmail.com</t>
+          <t>delongla36@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kukkonen</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>dave.kukkonen@gmail.com</t>
+          <t>mzjonesey@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Deanna</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sundberg</t>
+          <t>Kukkonen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>deanna@teamfussyhussey.ca</t>
+          <t>dave.kukkonen@gmail.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Deanna</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Sundberg</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ajones19@hotmail.ca</t>
+          <t>deanna@teamfussyhussey.ca</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Robby</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>robbymachadoramos@gmail.com</t>
+          <t>ajones19@hotmail.ca</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stacy</t>
+          <t>Robby</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Merriam</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>smerriam44@icloud.com</t>
+          <t>robbymachadoramos@gmail.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Stacy</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Merriam</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>noahschaly@gmail.com</t>
+          <t>smerriam44@icloud.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Harry</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pittman</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>harrythesteelstudman@gmail.com</t>
+          <t>noahschaly@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Harry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Pittman</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sdclark1956@gmail.com</t>
+          <t>harrythesteelstudman@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hutchinson</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>amy.h@safestart.com</t>
+          <t>sdclark1956@gmail.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lesage</t>
+          <t>Hutchinson</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>pmlesage@gmail.com</t>
+          <t>amy.h@safestart.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Widling</t>
+          <t>Lesage</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>karenwidling@gmail.com</t>
+          <t>pmlesage@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Isbester</t>
+          <t>Bangco</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>michelle@orkneyresidential.ca</t>
+          <t>leonardbangco@gmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nigel</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baigent</t>
+          <t>Widling</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nigel@canadianwindowcompany.ca</t>
+          <t>karenwidling@gmail.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Conlon</t>
+          <t>Isbester</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>conlon.lachlan@gmail.com</t>
+          <t>michelle@orkneyresidential.ca</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Nigel</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Humber</t>
+          <t>Baigent</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>andrealouise@icloud.com</t>
+          <t>nigel@canadianwindowcompany.ca</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cimprich</t>
+          <t>Conlon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ritasretreat@outlook.com</t>
+          <t>conlon.lachlan@gmail.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hydamen</t>
+          <t>Humber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>abcdef&amp;&amp;@icloud.com</t>
+          <t>andrealouise@icloud.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Kaelan</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Cimprich</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>kaelanfraser@gmail.com</t>
+          <t>ritasretreat@outlook.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Hydamen</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>davidsonconnor40@gmail.com</t>
+          <t>abcdef&amp;&amp;@icloud.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Kaelan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Teves</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>steveteves@hotmail.com</t>
+          <t>kaelanfraser@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Botts</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Botterill</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>botts@pickleplexclub.ca</t>
+          <t>davidsonconnor40@gmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,15 +2019,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cadavid</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Teves</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>steveteves@hotmail.com</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2037,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Botts</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lorenzoni</t>
+          <t>Botterill</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>liz.a.lorenzoni@gmail.com</t>
+          <t>botts@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2059,12 +2063,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Cadavid</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -2077,15 +2081,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walton</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Lorenzoni</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>liz.a.lorenzoni@gmail.com</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2095,12 +2103,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>O'Coin</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2113,12 +2121,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>O'Coin</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2131,7 +2139,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ember</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2149,7 +2157,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2167,12 +2175,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ember</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Caletti</t>
+          <t>O'Coin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2185,12 +2193,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rudra</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>O'Coin</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2203,12 +2211,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Caletti</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2221,12 +2229,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Rudra</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2239,12 +2247,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mya</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2257,12 +2265,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2275,12 +2283,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Brettley</t>
+          <t>Mya</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Surerus</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2293,12 +2301,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2311,12 +2319,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Rylan</t>
+          <t>Brettley</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Surerus</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2329,12 +2337,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ALYSSA</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2347,12 +2355,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Rylan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2365,12 +2373,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>ALYSSA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2383,12 +2391,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2401,12 +2409,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2419,12 +2427,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2437,12 +2445,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Barrett</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LaPalm</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2455,12 +2463,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>McNulty</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2473,12 +2481,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Barrett</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Goldsmith</t>
+          <t>LaPalm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2491,12 +2499,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Haylen</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foote</t>
+          <t>McNulty</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2509,12 +2517,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Goldsmith</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2527,12 +2535,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bethany</t>
+          <t>Haylen</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Foote</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2545,12 +2553,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Misty</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2563,12 +2571,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Bethany</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mamajek</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2581,12 +2589,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Dinah</t>
+          <t>Misty</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ramin</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2599,12 +2607,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Lyla</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Mamajek</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2617,12 +2625,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Dinah</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tipper</t>
+          <t>Ramin</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2635,12 +2643,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Lyla</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2653,12 +2661,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Tipper</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2671,12 +2679,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2689,12 +2697,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2707,12 +2715,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Moira</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2725,12 +2733,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Hart</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2743,12 +2751,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Moira</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2761,12 +2769,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2779,12 +2787,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2797,12 +2805,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2815,12 +2823,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2833,12 +2841,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Juliet</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2851,12 +2859,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2869,12 +2877,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jameel</t>
+          <t>Juliet</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2887,12 +2895,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pendleton</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2905,12 +2913,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Jameel</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2923,12 +2931,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Pendleton</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2941,12 +2949,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Neeson</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Fournier</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2959,12 +2967,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cyril</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2977,12 +2985,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Neeson</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2995,12 +3003,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>Cyril</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3013,12 +3021,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bassett-Spiers</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3031,12 +3039,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3049,12 +3057,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Keith</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Roberton</t>
+          <t>Bassett-Spiers</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3067,12 +3075,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>nathan</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3085,12 +3093,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Blythe</t>
+          <t>Keith</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Crowley</t>
+          <t>Roberton</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3103,12 +3111,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>nathan</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3121,12 +3129,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>greg</t>
+          <t>Blythe</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Papakiriazis</t>
+          <t>Crowley</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3139,12 +3147,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3157,12 +3165,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Marley</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Philp</t>
+          <t>Papakiriazis</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3175,12 +3183,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Penney</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3193,12 +3201,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Marley</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Philp</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3211,12 +3219,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Jadyn</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Brouillard</t>
+          <t>Penney</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3229,12 +3237,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3247,12 +3255,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Jadyn</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vreugdenhil</t>
+          <t>Brouillard</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3265,12 +3273,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3283,12 +3291,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Domiguiano</t>
+          <t>Vreugdenhil</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3301,12 +3309,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3319,12 +3327,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Domiguiano</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3337,12 +3345,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Yasmeen</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3355,12 +3363,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3373,12 +3381,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Yasmeen</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3391,12 +3399,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3409,12 +3417,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Di Sandolo</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3427,12 +3435,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3445,12 +3453,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tetlock</t>
+          <t>Di Sandolo</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3463,12 +3471,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3481,12 +3489,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Dominguiano</t>
+          <t>Tetlock</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3499,12 +3507,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3517,12 +3525,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Gledhill</t>
+          <t>Dominguiano</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3535,12 +3543,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>McCullough</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3553,12 +3561,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Halligan</t>
+          <t>Gledhill</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3571,12 +3579,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>McCullough</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3589,12 +3597,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Halligan</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3607,12 +3615,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Burtnik</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3625,12 +3633,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Aliya</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Vriesema</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3643,12 +3651,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Burtnik</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3661,12 +3669,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cormac</t>
+          <t>Aliya</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Vriesema</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3679,12 +3687,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Angove</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3697,12 +3705,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Joey</t>
+          <t>Cormac</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3715,12 +3723,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Erica</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Angove</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3733,12 +3741,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Joey</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3751,12 +3759,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Erica</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3769,12 +3777,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3787,12 +3795,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Schier</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3805,12 +3813,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Henshaw</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3823,12 +3831,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Norris</t>
+          <t>Schier</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3841,12 +3849,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Julius</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>Henshaw</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3859,12 +3867,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Norris</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3877,12 +3885,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Julius</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3895,12 +3903,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3913,12 +3921,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Maracle</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3931,12 +3939,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Simpson</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3949,12 +3957,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Mccoy</t>
+          <t>Maracle</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3967,12 +3975,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>morgante</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3985,12 +3993,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Patry</t>
+          <t>Mccoy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4003,12 +4011,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Gleeson</t>
+          <t>morgante</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4021,12 +4029,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Grimes</t>
+          <t>Patry</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4039,7 +4047,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Rowen</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4057,12 +4065,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Davianna</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Grimes</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4075,12 +4083,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Rowen</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Gleeson</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4093,12 +4101,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Lilly</t>
+          <t>Davianna</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4111,12 +4119,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>hendrik</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4129,12 +4137,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Lilly</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4147,12 +4155,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>hendrik</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4165,12 +4173,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sacha</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Caritey</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4183,12 +4191,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Wallis</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4201,12 +4209,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Sacha</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Caritey</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4219,12 +4227,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>isaac</t>
+          <t>Wallis</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4237,12 +4245,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BHAVIK</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4255,12 +4263,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>isaac</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4273,12 +4281,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>will</t>
+          <t>BHAVIK</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4291,12 +4299,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Pixley</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4309,12 +4317,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Jamieson</t>
+          <t>will</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4327,12 +4335,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Pixley</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4345,12 +4353,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Jamieson</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Calvert-Challice</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4363,12 +4371,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4381,12 +4389,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Calvert</t>
+          <t>Calvert-Challice</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4399,12 +4407,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Alkina</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4417,19 +4425,15 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Riley</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>janetrileybowen@gmail.com</t>
-        </is>
-      </c>
+          <t>Calvert</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4439,12 +4443,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Alkina</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4457,15 +4461,19 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>vada</t>
+          <t>Janet</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>martin</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>janetrileybowen@gmail.com</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4475,12 +4483,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4493,12 +4501,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>vada</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Fajardo</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4511,12 +4519,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Zuwerkalow</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4529,12 +4537,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Fajardo</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4547,12 +4555,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Brett</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Zuwerkalow</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4565,12 +4573,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4583,12 +4591,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Brett</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kelly-Clarke</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4601,12 +4609,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4619,12 +4627,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Kelly-Clarke</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4637,12 +4645,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Jessy</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4655,12 +4663,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Sokaywatt</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4673,12 +4681,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Kole</t>
+          <t>Jessy</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Krueger</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4691,12 +4699,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Carley-Jo</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Sokaywatt</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4709,12 +4717,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Kole</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Krueger</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4727,12 +4735,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Xiaoyi</t>
+          <t>Carley-Jo</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4745,12 +4753,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Lyndsay</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4763,12 +4771,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Abraham</t>
+          <t>Xiaoyi</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4781,12 +4789,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Siraj</t>
+          <t>Lyndsay</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4799,12 +4807,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Maddox</t>
+          <t>Abraham</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4817,12 +4825,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Siraj</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Munday</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4835,12 +4843,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Maddox</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4853,12 +4861,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DiPietrantonio</t>
+          <t>Munday</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4871,12 +4879,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4889,12 +4897,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Cousins</t>
+          <t>DiPietrantonio</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4907,12 +4915,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -4925,12 +4933,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Clow</t>
+          <t>Cousins</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4943,12 +4951,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Faris</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -4961,12 +4969,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Clow</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -4979,12 +4987,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -4997,12 +5005,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Elora</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5015,12 +5023,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5033,12 +5041,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Elora</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5051,12 +5059,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Walton</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5069,12 +5077,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Mulligan-Anderson</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5087,12 +5095,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Smolders</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5105,12 +5113,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Mulligan-Anderson</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5123,12 +5131,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Beccah</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Le Marchant</t>
+          <t>Smolders</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5141,12 +5149,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Xi</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5159,12 +5167,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Audrey-Mae</t>
+          <t>Beccah</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Le Marchant</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5177,12 +5185,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Xi</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Mallory</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5195,12 +5203,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Audrey-Mae</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Munroe</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5213,12 +5221,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Mallory</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5231,12 +5239,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Holbrough</t>
+          <t>Munroe</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5249,12 +5257,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5267,12 +5275,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Bucknell</t>
+          <t>Holbrough</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5285,12 +5293,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bonacci</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5303,12 +5311,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Callie</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Bucknell</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5321,12 +5329,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Charlee</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Quinn-Black</t>
+          <t>Bonacci</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5339,12 +5347,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Madi</t>
+          <t>Callie</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5357,12 +5365,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Charlee</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Pettey</t>
+          <t>Quinn-Black</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5375,12 +5383,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Madi</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5393,12 +5401,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Penn</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Pettey</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5411,12 +5419,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Poskin</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5429,12 +5437,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5447,12 +5455,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ewan</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Dahle</t>
+          <t>Poskin</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5465,12 +5473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5483,12 +5491,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Ewan</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Dahle</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5501,12 +5509,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5519,12 +5527,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Pang</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5537,12 +5545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Pang</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5555,17 +5563,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Lindon</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Roguel</t>
+          <t>Zhuo</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>j2x.roguel@gmail.com</t>
+          <t>lindonzhuo@gmail.com</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5577,15 +5585,19 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Maclean</t>
+          <t>Trizzia</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>trizziadelfin@gmail.com</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5595,15 +5607,19 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
+          <t>Cardenas</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>e_a_c_s@hotmail.com</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5613,12 +5629,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Eleanora</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Gigante</t>
+          <t>Pang</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5631,12 +5647,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Everett</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Pang</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5649,15 +5665,19 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Liliana</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Gigante</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr"/>
+          <t>Roguel</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>j2x.roguel@gmail.com</t>
+        </is>
+      </c>
       <c r="D274" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5667,12 +5687,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Lorie</t>
+          <t>Maclean</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Fuschino</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5685,12 +5705,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Giuliana</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Fuschino</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5703,12 +5723,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Dominic</t>
+          <t>Eleanora</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Fuschino</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5721,12 +5741,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Everett</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Holloway</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5739,12 +5759,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>keira</t>
+          <t>Liliana</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Hansford</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -5757,12 +5777,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>reese</t>
+          <t>Lorie</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Hansford</t>
+          <t>Fuschino</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5775,12 +5795,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>alina</t>
+          <t>Giuliana</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>bankole</t>
+          <t>Fuschino</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5793,12 +5813,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>yestin miles</t>
+          <t>Dominic</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>del prado</t>
+          <t>Fuschino</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5811,19 +5831,15 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Procunier</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>procuniermichael@gmail.com</t>
-        </is>
-      </c>
+          <t>Holloway</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5833,19 +5849,15 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>keira</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dufresne</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>laurie.dufrsne@icloud.com</t>
-        </is>
-      </c>
+          <t>Hansford</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5855,12 +5867,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Gerard</t>
+          <t>reese</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Dufresne</t>
+          <t>Hansford</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5873,12 +5885,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>alina</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>mckee</t>
+          <t>bankole</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -5891,12 +5903,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>gavin</t>
+          <t>yestin miles</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>mcleod</t>
+          <t>del prado</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -5909,17 +5921,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Procunier</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>jaaon@kgreid.ca</t>
+          <t>procuniermichael@gmail.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -5931,15 +5943,19 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Fintan</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Troy</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
+          <t>Dufresne</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>laurie.dufrsne@icloud.com</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5949,19 +5965,15 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Weston</t>
+          <t>Gerard</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Mayer</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>kfkmayer@gmail.com</t>
-        </is>
-      </c>
+          <t>Dufresne</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5971,12 +5983,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>chavez</t>
+          <t>mckee</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -5989,12 +6001,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>gavin</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>chavez</t>
+          <t>mcleod</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6007,17 +6019,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>milanvanessamay05@gmail.com</t>
+          <t>jaaon@kgreid.ca</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6029,12 +6041,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Stori</t>
+          <t>Fintan</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Crawford</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6047,15 +6059,19 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Weston</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Bostock</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr"/>
+          <t>Mayer</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>kfkmayer@gmail.com</t>
+        </is>
+      </c>
       <c r="D295" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6065,12 +6081,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>lennon</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>mawer</t>
+          <t>chavez</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6083,12 +6099,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>mawer</t>
+          <t>chavez</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -6101,15 +6117,19 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>moore</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>milanvanessamay05@gmail.com</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6119,12 +6139,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Stori</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Elson</t>
+          <t>Crawford</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6137,19 +6157,15 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Kirsti</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Stubbs</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>kirstistubbs@gmail.com</t>
-        </is>
-      </c>
+          <t>Bostock</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6159,12 +6175,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sean</t>
+          <t>lennon</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>elson</t>
+          <t>mawer</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6177,12 +6193,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Islah</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>O'Prey</t>
+          <t>mawer</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6195,12 +6211,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Norah</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>O'Prey</t>
+          <t>moore</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6213,12 +6229,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Wreni</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Crawford</t>
+          <t>Elson</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6231,15 +6247,19 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Kolten</t>
+          <t>Kirsti</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>McDougall</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
+          <t>Stubbs</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>kirstistubbs@gmail.com</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6249,12 +6269,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>sean</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>boyce</t>
+          <t>elson</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6267,12 +6287,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Gurbaaj</t>
+          <t>Islah</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>warya</t>
+          <t>O'Prey</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6285,12 +6305,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Gurlaal</t>
+          <t>Norah</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Warya</t>
+          <t>O'Prey</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6303,12 +6323,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>noah</t>
+          <t>Wreni</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>pouliot</t>
+          <t>Crawford</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6321,12 +6341,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Kolten</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>pouliot</t>
+          <t>McDougall</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6339,12 +6359,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Gyde</t>
+          <t>boyce</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6357,15 +6377,19 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Varun</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Bylaard</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr"/>
+          <t>Vaid</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>varun@ttkrealestateteam.com</t>
+        </is>
+      </c>
       <c r="D312" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6375,12 +6399,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Gurbaaj</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Bylaard</t>
+          <t>warya</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6393,19 +6417,15 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gurlaal</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>dkrawczyk@belleville.ca</t>
-        </is>
-      </c>
+          <t>Warya</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6415,12 +6435,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>noah</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Newar</t>
+          <t>pouliot</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6433,19 +6453,15 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Maracle</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>70spoldon@quintehealth.ca</t>
-        </is>
-      </c>
+          <t>pouliot</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6455,12 +6471,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Gyde</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6473,12 +6489,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Finley</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Bylaard</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6491,12 +6507,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Bylaard</t>
         </is>
       </c>
       <c r="C319" t="inlineStr"/>
@@ -6509,17 +6525,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Donna</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>duncand@hastingscounty.com</t>
+          <t>dkrawczyk@belleville.ca</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -6531,19 +6547,15 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Esau</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>sesau@belleville.ca</t>
-        </is>
-      </c>
+          <t>Newar</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6553,17 +6565,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Maracle</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>cindy.w@safestart.com</t>
+          <t>70spoldon@quintehealth.ca</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -6575,19 +6587,15 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Theresa</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>tgreen@hpedsb.on.ca</t>
-        </is>
-      </c>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6595,13 +6603,17 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr"/>
-      <c r="B324" t="inlineStr"/>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>tomg@bel-con.com</t>
-        </is>
-      </c>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Finley</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6611,19 +6623,15 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Muli</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>jmuli@cmhs-hpe.on.ca</t>
-        </is>
-      </c>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6631,11 +6639,19 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr"/>
-      <c r="B326" t="inlineStr"/>
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Joanne</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Klemencic</t>
+        </is>
+      </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>barryk@otgroup.ca</t>
+          <t>jk.klemencic@gmail.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -6647,17 +6663,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Donna</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Gretzky</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>agretzky@petersmithgm.com</t>
+          <t>duncand@hastingscounty.com</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -6669,17 +6685,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Esau</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>tedp@youthab.ca</t>
+          <t>sesau@belleville.ca</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -6691,15 +6707,19 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>daphne</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>quick</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr"/>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>cindy.w@safestart.com</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6709,15 +6729,19 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>bradley</t>
+          <t>Theresa</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>quick</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>tgreen@hpedsb.on.ca</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6725,19 +6749,11 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Sharon</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Adams</t>
-        </is>
-      </c>
+      <c r="A331" t="inlineStr"/>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="inlineStr">
         <is>
-          <t>rbough@qhc.on.ca</t>
+          <t>tomg@bel-con.com</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -6749,17 +6765,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Muli</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>michelle.garrard@bardonsupplies.com</t>
+          <t>jmuli@cmhs-hpe.on.ca</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -6769,19 +6785,11 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Bradley</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>Grant</t>
-        </is>
-      </c>
+      <c r="A333" t="inlineStr"/>
+      <c r="B333" t="inlineStr"/>
       <c r="C333" t="inlineStr">
         <is>
-          <t>bgrant@trianglefluid.com</t>
+          <t>barryk@otgroup.ca</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -6793,17 +6801,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Marchand</t>
+          <t>Gretzky</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>smarchand@maxwellpaper.ca</t>
+          <t>agretzky@petersmithgm.com</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -6815,17 +6823,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Seward</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>rseward@reidsdairy.com</t>
+          <t>tedp@youthab.ca</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -6835,13 +6843,17 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>maryanne.wooldridge@ceo.ymca.ca</t>
-        </is>
-      </c>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>daphne</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6851,19 +6863,15 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>bradley</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>mwhite@clbelleville.ca</t>
-        </is>
-      </c>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6873,17 +6881,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>crystal.johnston@ems-tech.net</t>
+          <t>rbough@qhc.on.ca</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -6893,11 +6901,19 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr"/>
-      <c r="B339" t="inlineStr"/>
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Garrard</t>
+        </is>
+      </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>eric@impacto.ca</t>
+          <t>michelle.garrard@bardonsupplies.com</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -6909,17 +6925,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Bradley</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Leonard-Free</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>aleonard-free@bellevilleps.ca</t>
+          <t>bgrant@trianglefluid.com</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -6931,17 +6947,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Alissa</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Partington</t>
+          <t>Marchand</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>apartington@cmhahpe.ca</t>
+          <t>smarchand@maxwellpaper.ca</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -6953,17 +6969,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Landan</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Burns-Keaney</t>
+          <t>Seward</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>landanb@pathwaysind.com</t>
+          <t>rseward@reidsdairy.com</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -6977,7 +6993,7 @@
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr">
         <is>
-          <t>aide@mix97.com</t>
+          <t>maryanne.wooldridge@ceo.ymca.ca</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -6989,17 +7005,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Juliana</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Finney</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>finneyj@hastingscounty.com</t>
+          <t>mwhite@clbelleville.ca</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7009,11 +7025,19 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr"/>
-      <c r="B345" t="inlineStr"/>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Crystal</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Johnston</t>
+        </is>
+      </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>loris.clarke@whitleynewman.com</t>
+          <t>crystal.johnston@ems-tech.net</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7027,7 +7051,7 @@
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>mmacdonald@jewelleng.ca</t>
+          <t>eric@impacto.ca</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7039,15 +7063,19 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Clack</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr"/>
+          <t>Leonard-Free</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>aleonard-free@bellevilleps.ca</t>
+        </is>
+      </c>
       <c r="D347" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7055,11 +7083,19 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr"/>
-      <c r="B348" t="inlineStr"/>
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Alissa</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Partington</t>
+        </is>
+      </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>thompsonellisk@bellevillesens.com</t>
+          <t>apartington@cmhahpe.ca</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7069,11 +7105,19 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr"/>
-      <c r="B349" t="inlineStr"/>
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Landan</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Burns-Keaney</t>
+        </is>
+      </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>nbowland@bcsautomation.ca</t>
+          <t>landanb@pathwaysind.com</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7083,19 +7127,11 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Sowmia</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Chalissery</t>
-        </is>
-      </c>
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="inlineStr">
         <is>
-          <t>schalissery@beclawat.com</t>
+          <t>aide@mix97.com</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7107,17 +7143,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Barb</t>
+          <t>Juliana</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Finney</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>barbcook@royallepage.ca</t>
+          <t>finneyj@hastingscounty.com</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7131,7 +7167,7 @@
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="inlineStr">
         <is>
-          <t>acooney@cooney.ca</t>
+          <t>loris.clarke@whitleynewman.com</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7141,19 +7177,11 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>Marvin</t>
-        </is>
-      </c>
+      <c r="A353" t="inlineStr"/>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>marvinj@bqwchc.com</t>
+          <t>mmacdonald@jewelleng.ca</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7165,19 +7193,15 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Gillis</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>sgillis@mcdougallinsurance.com</t>
-        </is>
-      </c>
+          <t>Clack</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7185,19 +7209,11 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Travis</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>Kupar</t>
-        </is>
-      </c>
+      <c r="A355" t="inlineStr"/>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>travis@truckright.ca</t>
+          <t>thompsonellisk@bellevillesens.com</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7207,19 +7223,11 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Stella</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>Haskin</t>
-        </is>
-      </c>
+      <c r="A356" t="inlineStr"/>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>shaskin@albertcollege.ca</t>
+          <t>nbowland@bcsautomation.ca</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -7229,11 +7237,19 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr"/>
-      <c r="B357" t="inlineStr"/>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Sowmia</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Chalissery</t>
+        </is>
+      </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>kcrowe@alarmsys.com</t>
+          <t>schalissery@beclawat.com</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -7243,11 +7259,19 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr"/>
-      <c r="B358" t="inlineStr"/>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Barb</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>james.hunt@ucbradio.com</t>
+          <t>barbcook@royallepage.ca</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7257,19 +7281,11 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Radhika</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>Sharma</t>
-        </is>
-      </c>
+      <c r="A359" t="inlineStr"/>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
-          <t>radhika@loyalistcollege.com</t>
+          <t>acooney@cooney.ca</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -7281,17 +7297,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Kessel</t>
+          <t>Marvin</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>christofere@metaservices.ca</t>
+          <t>marvinj@bqwchc.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7301,11 +7317,19 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr"/>
-      <c r="B361" t="inlineStr"/>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Gillis</t>
+        </is>
+      </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>akeys@emhware.com</t>
+          <t>sgillis@mcdougallinsurance.com</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -7317,17 +7341,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Lavanna</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Luong</t>
+          <t>Kupar</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>lavanna.luong@highlandshorescas.com</t>
+          <t>travis@truckright.ca</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -7337,11 +7361,19 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr"/>
-      <c r="B363" t="inlineStr"/>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Stella</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Haskin</t>
+        </is>
+      </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>tim@jaatsolutions.com</t>
+          <t>shaskin@albertcollege.ca</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7351,19 +7383,11 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Cherie</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>Horschman</t>
-        </is>
-      </c>
+      <c r="A364" t="inlineStr"/>
+      <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr">
         <is>
-          <t>cherie.horschman@heliahealthcare.com</t>
+          <t>kcrowe@alarmsys.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7373,17 +7397,13 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Antoine</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr"/>
+      <c r="A365" t="inlineStr"/>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>james.hunt@ucbradio.com</t>
+        </is>
+      </c>
       <c r="D365" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7393,15 +7413,19 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Radhika</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr"/>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>radhika@loyalistcollege.com</t>
+        </is>
+      </c>
       <c r="D366" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7411,15 +7435,19 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>zanette</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr"/>
+          <t>Kessel</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>christofere@metaservices.ca</t>
+        </is>
+      </c>
       <c r="D367" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7427,17 +7455,13 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Nathan</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr"/>
+      <c r="A368" t="inlineStr"/>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>akeys@emhware.com</t>
+        </is>
+      </c>
       <c r="D368" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7447,15 +7471,19 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>owen</t>
+          <t>Lavanna</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>lindsay</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr"/>
+          <t>Luong</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>lavanna.luong@highlandshorescas.com</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7463,17 +7491,13 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Alexandra</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr"/>
+      <c r="A370" t="inlineStr"/>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>tim@jaatsolutions.com</t>
+        </is>
+      </c>
       <c r="D370" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7483,17 +7507,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>TARAH</t>
+          <t>Cherie</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
+          <t>Horschman</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>bellevillebearcatsu18a@gmail.com</t>
+          <t>cherie.horschman@heliahealthcare.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7505,12 +7529,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Ramlochan</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -7523,12 +7547,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>myron</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>ibrahim</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -7541,12 +7565,12 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>ibrahim</t>
+          <t>zanette</t>
         </is>
       </c>
       <c r="C374" t="inlineStr"/>
@@ -7559,12 +7583,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -7577,16 +7601,1400 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>owen</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>lindsay</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Picard</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>TARAH</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>bellevillebearcatsu18a@gmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Ramlochan</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>myron</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ibrahim</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>mateo</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ibrahim</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Bohdan</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Maureen</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Gregorio</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>maureen.gregorio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Aleesha</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Siddiqi</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>siddiqi.aleesha@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Haskins</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>shaskins321@gmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Haskins</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>emma.haskins@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Allen</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Shackleton</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>shackleton.at@gmail.com</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>jordanmillerjune20@gmail.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Dufour</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>nicolas.dufour@gmail.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Beverly</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Mann</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>beverly924@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Andrea</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Shackleton</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>shackleton.ac@gmail.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Scott</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Cull</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>cullscott@gmail.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Chad</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Nolan</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>agilesamurai7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Michal</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Rajczewski</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>rajczewskim@gmail.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>christine</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>cull</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>christinecull33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Nicole</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Lamoureux</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>ronirejo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Aylen</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Garcia</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>aylengarseeya@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Bronwyn</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>McGeachy</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>bronwynmcgeachy@gmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Dante</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Palango</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>dante.palango@gmail.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Nolan</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Ramsay</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>campbellmel@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>jlp8353@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>calebjechung@gmail.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Bennett</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Ramsay</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>melanieramsay7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>LaPalm</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>jasonlapalm@gmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Eliza</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Capps-Perry</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>cmc23@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Tess</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Shakell</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>shakelltess@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>jposty38@gmail.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>isabelle</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>chaput</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>isabellechaput1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Maude</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Dufour</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>maudedufour07@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>AUSTIN</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>GENEREAUX</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>kngsfan072007@gmail.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>sarah</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>dufour</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>sarahdufour06@gmail.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>charles</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>dufour</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>charlesdufour04@gmail.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Gould</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>rebeccajoegould@gmail.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Aubrey</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>red_14santos@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Newman</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>bennboss18@gmail.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Pickett</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>henryjpickett@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Reisman</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>cedarreisman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>truaisch</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>jptruaisch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>noah.brown42@icloud.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Patrick</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Pickett</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>patrickdpickett@gmail.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Bruce</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Samis</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>michaelsamis18@gmail.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Tom</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Hanna</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>thomas_hanna77@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Gurbir</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Osahan</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>osahang@gmail.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Pickett</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>pickett.thomas@gmail.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Matias</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Veiga</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>matias.veiga24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Pickett</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>mccaughen@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Boadway</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>thomasboadway2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Sydona</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Elliott</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>sydona.elliott55@gmail.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>meech</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>taylor_meech@outlook.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Kylee</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Suraci</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>kyleekylend@gmail.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>kostin</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>blakely</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>shawnchambers20221@gmail.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Lachlann</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Bremner</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>lachlanbremner@gmail.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Erin</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Cennelly</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>cennelly.weld@gmail.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>ellie</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>elliew8896@gmail.com</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>hong</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>hongli8017@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Manley</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>manleyjack628@gmail.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Thorin</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>bremner</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>nmcdougall16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>montie</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>foxwell</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>montie@ibeam.ca</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Deke</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Osterhout</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>dekeo1507@gmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Belleville.xlsx
+++ b/docs/downloads/Belleville.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D440"/>
+  <dimension ref="A1:D454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Botts</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Botterill</t>
+          <t>Bowman</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>botts@pickleplexclub.ca</t>
+          <t>nickbowman2009@hotmail.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,15 +2063,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Botts</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cadavid</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Botterill</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>botts@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2081,17 +2085,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lorenzoni</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>liz.a.lorenzoni@gmail.com</t>
+          <t>anntownsend@outlook.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2103,12 +2107,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Cadavid</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2121,15 +2125,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Walton</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>Lorenzoni</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>liz.a.lorenzoni@gmail.com</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2139,12 +2147,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>O'Coin</t>
+          <t>Fulton</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2157,12 +2165,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>O'Coin</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2175,7 +2183,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ember</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2193,7 +2201,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2211,12 +2219,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Ember</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Caletti</t>
+          <t>O'Coin</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2229,12 +2237,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Rudra</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>O'Coin</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2247,12 +2255,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Caletti</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2265,12 +2273,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Rudra</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2283,12 +2291,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mya</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2301,12 +2309,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2319,12 +2327,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Brettley</t>
+          <t>Mya</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Surerus</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2337,12 +2345,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2355,12 +2363,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Rylan</t>
+          <t>Brettley</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Surerus</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2373,12 +2381,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ALYSSA</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2391,12 +2399,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Rylan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2409,12 +2417,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>ALYSSA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2427,12 +2435,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2445,12 +2453,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2463,12 +2471,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2481,12 +2489,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Barrett</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LaPalm</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2499,12 +2507,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>McNulty</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2517,12 +2525,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Barrett</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Goldsmith</t>
+          <t>LaPalm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2535,12 +2543,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Haylen</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foote</t>
+          <t>McNulty</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2553,12 +2561,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Goldsmith</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2571,12 +2579,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bethany</t>
+          <t>Haylen</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Foote</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2589,12 +2597,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Misty</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2607,12 +2615,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Bethany</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mamajek</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2625,12 +2633,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Dinah</t>
+          <t>Misty</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ramin</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2643,12 +2651,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Lyla</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Mamajek</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2661,12 +2669,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Dinah</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tipper</t>
+          <t>Ramin</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2679,12 +2687,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Lyla</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2697,12 +2705,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Tipper</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2715,12 +2723,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2733,12 +2741,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2751,12 +2759,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Moira</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2769,12 +2777,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Hart</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2787,12 +2795,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Moira</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2805,12 +2813,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2823,12 +2831,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2841,12 +2849,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2859,12 +2867,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2877,12 +2885,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Juliet</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2895,12 +2903,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2913,12 +2921,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Jameel</t>
+          <t>Juliet</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2931,12 +2939,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pendleton</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2949,12 +2957,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Jameel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2967,12 +2975,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Pendleton</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2985,12 +2993,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Neeson</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Fournier</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3003,12 +3011,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cyril</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3021,12 +3029,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Neeson</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3039,12 +3047,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>Cyril</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3057,12 +3065,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bassett-Spiers</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3075,12 +3083,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3093,12 +3101,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Keith</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Roberton</t>
+          <t>Bassett-Spiers</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3111,12 +3119,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>nathan</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3129,12 +3137,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Blythe</t>
+          <t>Keith</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Crowley</t>
+          <t>Roberton</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3147,12 +3155,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>nathan</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3165,12 +3173,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>greg</t>
+          <t>Blythe</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Papakiriazis</t>
+          <t>Crowley</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3183,12 +3191,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3201,12 +3209,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Marley</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Philp</t>
+          <t>Papakiriazis</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3219,12 +3227,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Penney</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3237,12 +3245,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Marley</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Philp</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3255,12 +3263,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Jadyn</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Brouillard</t>
+          <t>Penney</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3273,12 +3281,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3291,12 +3299,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Jadyn</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vreugdenhil</t>
+          <t>Brouillard</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3309,12 +3317,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3327,12 +3335,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Domiguiano</t>
+          <t>Vreugdenhil</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3345,12 +3353,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3363,12 +3371,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Domiguiano</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3381,12 +3389,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Yasmeen</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3399,12 +3407,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3417,12 +3425,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Yasmeen</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3435,12 +3443,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3453,12 +3461,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Di Sandolo</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3471,12 +3479,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3489,12 +3497,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tetlock</t>
+          <t>Di Sandolo</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3507,12 +3515,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3525,12 +3533,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Dominguiano</t>
+          <t>Tetlock</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3543,12 +3551,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3561,12 +3569,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Gledhill</t>
+          <t>Dominguiano</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3579,12 +3587,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>McCullough</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3597,12 +3605,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Halligan</t>
+          <t>Gledhill</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3615,12 +3623,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>McCullough</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3633,12 +3641,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Halligan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3651,12 +3659,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Burtnik</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3669,12 +3677,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Aliya</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Vriesema</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3687,12 +3695,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Burtnik</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3705,12 +3713,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cormac</t>
+          <t>Aliya</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Vriesema</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3723,12 +3731,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Angove</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3741,12 +3749,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Joey</t>
+          <t>Cormac</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3759,12 +3767,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Erica</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Angove</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3777,12 +3785,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Joey</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3795,12 +3803,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Erica</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3813,12 +3821,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3831,12 +3839,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Schier</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3849,12 +3857,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Henshaw</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3867,12 +3875,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Norris</t>
+          <t>Schier</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3885,12 +3893,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Julius</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>Henshaw</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3903,12 +3911,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Norris</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3921,12 +3929,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Julius</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3939,12 +3947,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3957,12 +3965,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Maracle</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3975,12 +3983,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Simpson</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -3993,12 +4001,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mccoy</t>
+          <t>Maracle</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4011,12 +4019,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>morgante</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4029,12 +4037,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Patry</t>
+          <t>Mccoy</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4047,12 +4055,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Gleeson</t>
+          <t>morgante</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4065,12 +4073,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Grimes</t>
+          <t>Patry</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4083,7 +4091,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Rowen</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4101,12 +4109,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Davianna</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Grimes</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4119,12 +4127,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Rowen</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Gleeson</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4137,12 +4145,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Lilly</t>
+          <t>Davianna</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4155,12 +4163,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>hendrik</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4173,12 +4181,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Lilly</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4191,12 +4199,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>hendrik</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4209,12 +4217,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Sacha</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Caritey</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4227,12 +4235,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Wallis</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4245,12 +4253,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>Sacha</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Caritey</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4263,12 +4271,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>isaac</t>
+          <t>Wallis</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4281,12 +4289,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BHAVIK</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4299,12 +4307,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>isaac</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4317,12 +4325,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>will</t>
+          <t>BHAVIK</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4335,12 +4343,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Pixley</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4353,12 +4361,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Jamieson</t>
+          <t>will</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4371,12 +4379,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Pixley</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4389,12 +4397,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Jamieson</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Calvert-Challice</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4407,12 +4415,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4425,12 +4433,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Calvert</t>
+          <t>Calvert-Challice</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4443,12 +4451,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Alkina</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4461,19 +4469,15 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Riley</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>janetrileybowen@gmail.com</t>
-        </is>
-      </c>
+          <t>Calvert</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4483,12 +4487,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>Alkina</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4501,15 +4505,19 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>vada</t>
+          <t>Janet</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>martin</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>janetrileybowen@gmail.com</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4519,12 +4527,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4537,12 +4545,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>vada</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Fajardo</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4555,12 +4563,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Zuwerkalow</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4573,12 +4581,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Fajardo</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4591,12 +4599,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Brett</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Zuwerkalow</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4609,12 +4617,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4627,12 +4635,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Brett</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Kelly-Clarke</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4645,12 +4653,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4663,12 +4671,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Kelly-Clarke</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4681,12 +4689,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Jessy</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4699,12 +4707,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Sokaywatt</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4717,12 +4725,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Kole</t>
+          <t>Jessy</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Krueger</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4735,12 +4743,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Carley-Jo</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Sokaywatt</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4753,12 +4761,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Kole</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Krueger</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4771,12 +4779,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Xiaoyi</t>
+          <t>Carley-Jo</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4789,12 +4797,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Lyndsay</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4807,12 +4815,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Abraham</t>
+          <t>Xiaoyi</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4825,12 +4833,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Siraj</t>
+          <t>Lyndsay</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4843,12 +4851,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Maddox</t>
+          <t>Abraham</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4861,12 +4869,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Siraj</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Munday</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4879,12 +4887,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Maddox</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4897,12 +4905,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DiPietrantonio</t>
+          <t>Munday</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4915,12 +4923,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -4933,12 +4941,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Cousins</t>
+          <t>DiPietrantonio</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4951,12 +4959,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -4969,12 +4977,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Clow</t>
+          <t>Cousins</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -4987,12 +4995,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Faris</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5005,12 +5013,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Clow</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5023,12 +5031,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5041,12 +5049,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Elora</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5059,12 +5067,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5077,12 +5085,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Elora</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5095,12 +5103,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Walton</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5113,12 +5121,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Mulligan-Anderson</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5131,12 +5139,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Smolders</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5149,12 +5157,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Mulligan-Anderson</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5167,12 +5175,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Beccah</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Le Marchant</t>
+          <t>Smolders</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5185,12 +5193,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Xi</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5203,12 +5211,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Audrey-Mae</t>
+          <t>Beccah</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Le Marchant</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5221,12 +5229,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Xi</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Mallory</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5239,12 +5247,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Audrey-Mae</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Munroe</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5257,12 +5265,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Mallory</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5275,12 +5283,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Holbrough</t>
+          <t>Munroe</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5293,12 +5301,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5311,12 +5319,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Bucknell</t>
+          <t>Holbrough</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5329,12 +5337,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Bonacci</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5347,12 +5355,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Callie</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Bucknell</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5365,12 +5373,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Charlee</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Quinn-Black</t>
+          <t>Bonacci</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5383,12 +5391,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Madi</t>
+          <t>Callie</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5401,12 +5409,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Charlee</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Pettey</t>
+          <t>Quinn-Black</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5419,12 +5427,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Madi</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5437,12 +5445,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Penn</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Pettey</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5455,12 +5463,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Poskin</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5473,12 +5481,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5491,12 +5499,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ewan</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Dahle</t>
+          <t>Poskin</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5509,12 +5517,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5527,12 +5535,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Ewan</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Dahle</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5545,12 +5553,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5563,19 +5571,15 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Lindon</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Zhuo</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>lindonzhuo@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilkinson</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5585,19 +5589,15 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Trizzia</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Delfin</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>trizziadelfin@gmail.com</t>
-        </is>
-      </c>
+          <t>Lupili</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5607,17 +5607,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Eduardo</t>
+          <t>Lindon</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Cardenas</t>
+          <t>Zhuo</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>e_a_c_s@hotmail.com</t>
+          <t>lindonzhuo@gmail.com</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -5629,15 +5629,19 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Trizzia</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Pang</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
+          <t>Delfin</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>trizziadelfin@gmail.com</t>
+        </is>
+      </c>
       <c r="D272" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5647,15 +5651,19 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Pang</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+          <t>Cardenas</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>e_a_c_s@hotmail.com</t>
+        </is>
+      </c>
       <c r="D273" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5665,19 +5673,15 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Joana</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Roguel</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>j2x.roguel@gmail.com</t>
-        </is>
-      </c>
+          <t>Pang</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5687,12 +5691,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Maclean</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Pang</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5705,15 +5709,19 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Joana</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
+          <t>Roguel</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>j2x.roguel@gmail.com</t>
+        </is>
+      </c>
       <c r="D276" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5723,12 +5731,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Eleanora</t>
+          <t>Maclean</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Gigante</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5741,7 +5749,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Everett</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -5759,7 +5767,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Liliana</t>
+          <t>Eleanora</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -5777,12 +5785,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Lorie</t>
+          <t>Everett</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Fuschino</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5795,12 +5803,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Giuliana</t>
+          <t>Liliana</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Fuschino</t>
+          <t>Gigante</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5813,7 +5821,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Dominic</t>
+          <t>Lorie</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -5831,12 +5839,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Giuliana</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Holloway</t>
+          <t>Fuschino</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5849,12 +5857,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>keira</t>
+          <t>Dominic</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Hansford</t>
+          <t>Fuschino</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -5867,12 +5875,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>reese</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Hansford</t>
+          <t>Holloway</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5885,12 +5893,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>alina</t>
+          <t>keira</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>bankole</t>
+          <t>Hansford</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -5903,12 +5911,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>yestin miles</t>
+          <t>reese</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>del prado</t>
+          <t>Hansford</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -5921,19 +5929,15 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>alina</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Procunier</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>procuniermichael@gmail.com</t>
-        </is>
-      </c>
+          <t>bankole</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5943,19 +5947,15 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>yestin miles</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Dufresne</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>laurie.dufrsne@icloud.com</t>
-        </is>
-      </c>
+          <t>del prado</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5965,15 +5965,19 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Gerard</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Dufresne</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr"/>
+          <t>Procunier</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>procuniermichael@gmail.com</t>
+        </is>
+      </c>
       <c r="D290" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5983,15 +5987,19 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ty</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>mckee</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr"/>
+          <t>Dufresne</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>laurie.dufrsne@icloud.com</t>
+        </is>
+      </c>
       <c r="D291" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6001,12 +6009,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>gavin</t>
+          <t>Gerard</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>mcleod</t>
+          <t>Dufresne</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6019,19 +6027,15 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>ty</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Reid</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>jaaon@kgreid.ca</t>
-        </is>
-      </c>
+          <t>mckee</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6041,12 +6045,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Fintan</t>
+          <t>gavin</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>mcleod</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6059,17 +6063,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Weston</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Mayer</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>kfkmayer@gmail.com</t>
+          <t>jaaon@kgreid.ca</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6081,12 +6085,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Fintan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>chavez</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6099,15 +6103,19 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Weston</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>chavez</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr"/>
+          <t>Mayer</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>kfkmayer@gmail.com</t>
+        </is>
+      </c>
       <c r="D297" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6117,19 +6125,15 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>milanvanessamay05@gmail.com</t>
-        </is>
-      </c>
+          <t>chavez</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6139,12 +6143,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Stori</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Crawford</t>
+          <t>chavez</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6157,15 +6161,19 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Bostock</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>milanvanessamay05@gmail.com</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6175,12 +6183,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>lennon</t>
+          <t>Stori</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>mawer</t>
+          <t>Crawford</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6193,12 +6201,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>mawer</t>
+          <t>Bostock</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6211,12 +6219,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>lennon</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>moore</t>
+          <t>mawer</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6229,12 +6237,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Elson</t>
+          <t>mawer</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6247,19 +6255,15 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Kirsti</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Stubbs</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>kirstistubbs@gmail.com</t>
-        </is>
-      </c>
+          <t>moore</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6269,12 +6273,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sean</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>elson</t>
+          <t>Elson</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
@@ -6287,15 +6291,19 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Islah</t>
+          <t>Kirsti</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>O'Prey</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr"/>
+          <t>Stubbs</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>kirstistubbs@gmail.com</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6305,12 +6313,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Norah</t>
+          <t>sean</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>O'Prey</t>
+          <t>elson</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6323,12 +6331,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Wreni</t>
+          <t>Islah</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Crawford</t>
+          <t>O'Prey</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6341,12 +6349,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Kolten</t>
+          <t>Norah</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>McDougall</t>
+          <t>O'Prey</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6359,12 +6367,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Wreni</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>boyce</t>
+          <t>Crawford</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6377,19 +6385,15 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>Kolten</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Vaid</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>varun@ttkrealestateteam.com</t>
-        </is>
-      </c>
+          <t>McDougall</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6399,12 +6403,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Gurbaaj</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>warya</t>
+          <t>boyce</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6417,15 +6421,19 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Gurlaal</t>
+          <t>Varun</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Warya</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr"/>
+          <t>Vaid</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>varun@ttkrealestateteam.com</t>
+        </is>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6435,12 +6443,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>noah</t>
+          <t>Gurbaaj</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>pouliot</t>
+          <t>warya</t>
         </is>
       </c>
       <c r="C315" t="inlineStr"/>
@@ -6453,12 +6461,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Mathis</t>
+          <t>Gurlaal</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>pouliot</t>
+          <t>Warya</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6471,12 +6479,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>noah</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Gyde</t>
+          <t>pouliot</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6489,12 +6497,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Frank</t>
+          <t>Mathis</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Bylaard</t>
+          <t>pouliot</t>
         </is>
       </c>
       <c r="C318" t="inlineStr"/>
@@ -6507,15 +6515,19 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Gary</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Bylaard</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr"/>
+          <t>Makrevski</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>kjmakrev@hotmail.com</t>
+        </is>
+      </c>
       <c r="D319" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6525,19 +6537,15 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>dkrawczyk@belleville.ca</t>
-        </is>
-      </c>
+          <t>Gyde</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6547,12 +6555,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>Frank</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Newar</t>
+          <t>Bylaard</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6565,19 +6573,15 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Gary</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Maracle</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>70spoldon@quintehealth.ca</t>
-        </is>
-      </c>
+          <t>Bylaard</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6587,15 +6591,19 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Macdonald</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr"/>
+          <t>Krawczyk</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>dkrawczyk@belleville.ca</t>
+        </is>
+      </c>
       <c r="D323" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6605,12 +6613,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Finley</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Newar</t>
         </is>
       </c>
       <c r="C324" t="inlineStr"/>
@@ -6623,15 +6631,19 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr"/>
+          <t>Maracle</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>70spoldon@quintehealth.ca</t>
+        </is>
+      </c>
       <c r="D325" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6641,19 +6653,15 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Klemencic</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>jk.klemencic@gmail.com</t>
-        </is>
-      </c>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6663,19 +6671,15 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Donna</t>
+          <t>Finley</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Duncan</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>duncand@hastingscounty.com</t>
-        </is>
-      </c>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6685,19 +6689,15 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Esau</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>sesau@belleville.ca</t>
-        </is>
-      </c>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6707,17 +6707,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Klemencic</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>cindy.w@safestart.com</t>
+          <t>jk.klemencic@gmail.com</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -6729,17 +6729,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Theresa</t>
+          <t>Donna</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>tgreen@hpedsb.on.ca</t>
+          <t>duncand@hastingscounty.com</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6749,11 +6749,19 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr"/>
-      <c r="B331" t="inlineStr"/>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Esau</t>
+        </is>
+      </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>tomg@bel-con.com</t>
+          <t>sesau@belleville.ca</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -6765,17 +6773,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Muli</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>jmuli@cmhs-hpe.on.ca</t>
+          <t>cindy.w@safestart.com</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -6785,11 +6793,19 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr"/>
-      <c r="B333" t="inlineStr"/>
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Theresa</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>barryk@otgroup.ca</t>
+          <t>tgreen@hpedsb.on.ca</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -6799,19 +6815,11 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Avery</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>Gretzky</t>
-        </is>
-      </c>
+      <c r="A334" t="inlineStr"/>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="inlineStr">
         <is>
-          <t>agretzky@petersmithgm.com</t>
+          <t>tomg@bel-con.com</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -6823,17 +6831,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Muli</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>tedp@youthab.ca</t>
+          <t>jmuli@cmhs-hpe.on.ca</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -6843,17 +6851,13 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>daphne</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>quick</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr"/>
+      <c r="A336" t="inlineStr"/>
+      <c r="B336" t="inlineStr"/>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>barryk@otgroup.ca</t>
+        </is>
+      </c>
       <c r="D336" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6863,15 +6867,19 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>bradley</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>quick</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
+          <t>Gretzky</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>agretzky@petersmithgm.com</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6881,17 +6889,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Adams</t>
+          <t>Parker</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>rbough@qhc.on.ca</t>
+          <t>tedp@youthab.ca</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -6903,19 +6911,15 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>daphne</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Garrard</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>michelle.garrard@bardonsupplies.com</t>
-        </is>
-      </c>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6925,19 +6929,15 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>bradley</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Grant</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>bgrant@trianglefluid.com</t>
-        </is>
-      </c>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6947,17 +6947,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Marchand</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>smarchand@maxwellpaper.ca</t>
+          <t>rbough@qhc.on.ca</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -6969,17 +6969,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Seward</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>rseward@reidsdairy.com</t>
+          <t>michelle.garrard@bardonsupplies.com</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -6989,11 +6989,19 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr"/>
-      <c r="B343" t="inlineStr"/>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Bradley</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Grant</t>
+        </is>
+      </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>maryanne.wooldridge@ceo.ymca.ca</t>
+          <t>bgrant@trianglefluid.com</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7005,17 +7013,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Marchand</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>mwhite@clbelleville.ca</t>
+          <t>smarchand@maxwellpaper.ca</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7027,17 +7035,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Johnston</t>
+          <t>Seward</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>crystal.johnston@ems-tech.net</t>
+          <t>rseward@reidsdairy.com</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7051,7 +7059,7 @@
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr">
         <is>
-          <t>eric@impacto.ca</t>
+          <t>maryanne.wooldridge@ceo.ymca.ca</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -7063,17 +7071,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Amber</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Leonard-Free</t>
+          <t>White</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>aleonard-free@bellevilleps.ca</t>
+          <t>mwhite@clbelleville.ca</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7085,17 +7093,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Alissa</t>
+          <t>Crystal</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Partington</t>
+          <t>Johnston</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>apartington@cmhahpe.ca</t>
+          <t>crystal.johnston@ems-tech.net</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7105,19 +7113,11 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Landan</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>Burns-Keaney</t>
-        </is>
-      </c>
+      <c r="A349" t="inlineStr"/>
+      <c r="B349" t="inlineStr"/>
       <c r="C349" t="inlineStr">
         <is>
-          <t>landanb@pathwaysind.com</t>
+          <t>eric@impacto.ca</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7127,11 +7127,19 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr"/>
-      <c r="B350" t="inlineStr"/>
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Amber</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Leonard-Free</t>
+        </is>
+      </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>aide@mix97.com</t>
+          <t>aleonard-free@bellevilleps.ca</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7143,17 +7151,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Juliana</t>
+          <t>Alissa</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Finney</t>
+          <t>Partington</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>finneyj@hastingscounty.com</t>
+          <t>apartington@cmhahpe.ca</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7163,11 +7171,19 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr"/>
-      <c r="B352" t="inlineStr"/>
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Landan</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Burns-Keaney</t>
+        </is>
+      </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>loris.clarke@whitleynewman.com</t>
+          <t>landanb@pathwaysind.com</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -7181,7 +7197,7 @@
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="inlineStr">
         <is>
-          <t>mmacdonald@jewelleng.ca</t>
+          <t>aide@mix97.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7193,15 +7209,19 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Juliana</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Clack</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr"/>
+          <t>Finney</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>finneyj@hastingscounty.com</t>
+        </is>
+      </c>
       <c r="D354" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7213,7 +7233,7 @@
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="inlineStr">
         <is>
-          <t>thompsonellisk@bellevillesens.com</t>
+          <t>loris.clarke@whitleynewman.com</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7227,7 +7247,7 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
-          <t>nbowland@bcsautomation.ca</t>
+          <t>mmacdonald@jewelleng.ca</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -7239,19 +7259,15 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Sowmia</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Chalissery</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>schalissery@beclawat.com</t>
-        </is>
-      </c>
+          <t>Clack</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7259,19 +7275,11 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Barb</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>Cook</t>
-        </is>
-      </c>
+      <c r="A358" t="inlineStr"/>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr">
         <is>
-          <t>barbcook@royallepage.ca</t>
+          <t>thompsonellisk@bellevillesens.com</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7285,7 +7293,7 @@
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
-          <t>acooney@cooney.ca</t>
+          <t>nbowland@bcsautomation.ca</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -7297,17 +7305,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Sowmia</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Marvin</t>
+          <t>Chalissery</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>marvinj@bqwchc.com</t>
+          <t>schalissery@beclawat.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7319,17 +7327,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Barb</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Gillis</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>sgillis@mcdougallinsurance.com</t>
+          <t>barbcook@royallepage.ca</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -7339,19 +7347,11 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Travis</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>Kupar</t>
-        </is>
-      </c>
+      <c r="A362" t="inlineStr"/>
+      <c r="B362" t="inlineStr"/>
       <c r="C362" t="inlineStr">
         <is>
-          <t>travis@truckright.ca</t>
+          <t>acooney@cooney.ca</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -7363,17 +7363,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Stella</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Haskin</t>
+          <t>Marvin</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>shaskin@albertcollege.ca</t>
+          <t>marvinj@bqwchc.com</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7383,11 +7383,19 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr"/>
-      <c r="B364" t="inlineStr"/>
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Gillis</t>
+        </is>
+      </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>kcrowe@alarmsys.com</t>
+          <t>sgillis@mcdougallinsurance.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7397,11 +7405,19 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr"/>
-      <c r="B365" t="inlineStr"/>
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Travis</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Kupar</t>
+        </is>
+      </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>james.hunt@ucbradio.com</t>
+          <t>travis@truckright.ca</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7413,17 +7429,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Radhika</t>
+          <t>Stella</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Haskin</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>radhika@loyalistcollege.com</t>
+          <t>shaskin@albertcollege.ca</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -7433,19 +7449,11 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Anthony</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>Kessel</t>
-        </is>
-      </c>
+      <c r="A367" t="inlineStr"/>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr">
         <is>
-          <t>christofere@metaservices.ca</t>
+          <t>kcrowe@alarmsys.com</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -7459,7 +7467,7 @@
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
         <is>
-          <t>akeys@emhware.com</t>
+          <t>james.hunt@ucbradio.com</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7471,17 +7479,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Lavanna</t>
+          <t>Radhika</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Luong</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>lavanna.luong@highlandshorescas.com</t>
+          <t>radhika@loyalistcollege.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7491,11 +7499,19 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr"/>
-      <c r="B370" t="inlineStr"/>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Kessel</t>
+        </is>
+      </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>tim@jaatsolutions.com</t>
+          <t>christofere@metaservices.ca</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -7505,19 +7521,11 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Cherie</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Horschman</t>
-        </is>
-      </c>
+      <c r="A371" t="inlineStr"/>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr">
         <is>
-          <t>cherie.horschman@heliahealthcare.com</t>
+          <t>akeys@emhware.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7529,15 +7537,19 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Lavanna</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr"/>
+          <t>Luong</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>lavanna.luong@highlandshorescas.com</t>
+        </is>
+      </c>
       <c r="D372" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7545,17 +7557,13 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Ellie</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr"/>
+      <c r="A373" t="inlineStr"/>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>tim@jaatsolutions.com</t>
+        </is>
+      </c>
       <c r="D373" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7565,15 +7573,19 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Cherie</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>zanette</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr"/>
+          <t>Horschman</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>cherie.horschman@heliahealthcare.com</t>
+        </is>
+      </c>
       <c r="D374" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7583,7 +7595,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -7601,12 +7613,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>owen</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>lindsay</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -7619,12 +7631,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Picard</t>
+          <t>zanette</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -7637,19 +7649,15 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>TARAH</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>bellevillebearcatsu18a@gmail.com</t>
-        </is>
-      </c>
+          <t>Picard</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7659,12 +7667,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>owen</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Ramlochan</t>
+          <t>lindsay</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -7677,12 +7685,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>myron</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ibrahim</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -7695,15 +7703,19 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>TARAH</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ibrahim</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>bellevillebearcatsu18a@gmail.com</t>
+        </is>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7713,12 +7725,12 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>Ramlochan</t>
         </is>
       </c>
       <c r="C382" t="inlineStr"/>
@@ -7731,12 +7743,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>myron</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>ibrahim</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -7749,19 +7761,15 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Gregorio</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>maureen.gregorio@gmail.com</t>
-        </is>
-      </c>
+          <t>ibrahim</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7771,19 +7779,15 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Aleesha</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>siddiqi.aleesha@gmail.com</t>
-        </is>
-      </c>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7793,19 +7797,15 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Bohdan</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Haskins</t>
-        </is>
-      </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>shaskins321@gmail.com</t>
-        </is>
-      </c>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7815,17 +7815,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Haskins</t>
+          <t>Gregorio</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>emma.haskins@hotmail.com</t>
+          <t>maureen.gregorio@gmail.com</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -7837,17 +7837,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Aleesha</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Shackleton</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>shackleton.at@gmail.com</t>
+          <t>siddiqi.aleesha@gmail.com</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -7859,17 +7859,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Haskins</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>jordanmillerjune20@gmail.com</t>
+          <t>shaskins321@gmail.com</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -7881,17 +7881,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>Haskins</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>nicolas.dufour@gmail.com</t>
+          <t>emma.haskins@hotmail.com</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -7903,17 +7903,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Beverly</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Shackleton</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>beverly924@hotmail.com</t>
+          <t>shackleton.at@gmail.com</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -7925,17 +7925,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Shackleton</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>shackleton.ac@gmail.com</t>
+          <t>jordanmillerjune20@gmail.com</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -7947,17 +7947,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Cull</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>cullscott@gmail.com</t>
+          <t>nicolas.dufour@gmail.com</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Beverly</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Mann</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>agilesamurai7@gmail.com</t>
+          <t>beverly924@hotmail.com</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Rajczewski</t>
+          <t>Shackleton</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>rajczewskim@gmail.com</t>
+          <t>shackleton.ac@gmail.com</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -8013,17 +8013,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>christine</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>cull</t>
+          <t>Cull</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>christinecull33@gmail.com</t>
+          <t>cullscott@gmail.com</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -8035,17 +8035,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Lamoureux</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>ronirejo@gmail.com</t>
+          <t>agilesamurai7@gmail.com</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -8057,17 +8057,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Aylen</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Rajczewski</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>aylengarseeya@gmail.com</t>
+          <t>rajczewskim@gmail.com</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -8079,17 +8079,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Bronwyn</t>
+          <t>christine</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>McGeachy</t>
+          <t>cull</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>bronwynmcgeachy@gmail.com</t>
+          <t>christinecull33@gmail.com</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -8101,17 +8101,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Dante</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Palango</t>
+          <t>Lamoureux</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>dante.palango@gmail.com</t>
+          <t>ronirejo@gmail.com</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -8123,17 +8123,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Aylen</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ramsay</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>campbellmel@hotmail.com</t>
+          <t>aylengarseeya@gmail.com</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -8145,17 +8145,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Bronwyn</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>McGeachy</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>jlp8353@yahoo.com</t>
+          <t>bronwynmcgeachy@gmail.com</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -8167,17 +8167,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Palango</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>calebjechung@gmail.com</t>
+          <t>dante.palango@gmail.com</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>melanieramsay7@gmail.com</t>
+          <t>campbellmel@hotmail.com</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -8211,17 +8211,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>LaPalm</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>jasonlapalm@gmail.com</t>
+          <t>jlp8353@yahoo.com</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -8233,17 +8233,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Eliza</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Capps-Perry</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>cmc23@hotmail.com</t>
+          <t>calebjechung@gmail.com</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -8255,17 +8255,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Tess</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Shakell</t>
+          <t>Ramsay</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>shakelltess@gmail.com</t>
+          <t>melanieramsay7@gmail.com</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -8277,17 +8277,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>LaPalm</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>jposty38@gmail.com</t>
+          <t>jasonlapalm@gmail.com</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -8299,17 +8299,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>isabelle</t>
+          <t>Eliza</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>chaput</t>
+          <t>Capps-Perry</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>isabellechaput1@gmail.com</t>
+          <t>cmc23@hotmail.com</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -8321,17 +8321,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Maude</t>
+          <t>Tess</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>Shakell</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>maudedufour07@gmail.com</t>
+          <t>shakelltess@gmail.com</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -8343,17 +8343,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>AUSTIN</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>GENEREAUX</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>kngsfan072007@gmail.com</t>
+          <t>jposty38@gmail.com</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -8365,17 +8365,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>sarah</t>
+          <t>isabelle</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>dufour</t>
+          <t>chaput</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>sarahdufour06@gmail.com</t>
+          <t>isabellechaput1@gmail.com</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -8387,17 +8387,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>charles</t>
+          <t>Maude</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>dufour</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>charlesdufour04@gmail.com</t>
+          <t>maudedufour07@gmail.com</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -8409,17 +8409,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>AUSTIN</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Gould</t>
+          <t>GENEREAUX</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>rebeccajoegould@gmail.com</t>
+          <t>kngsfan072007@gmail.com</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -8431,17 +8431,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>dufour</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>red_14santos@yahoo.com</t>
+          <t>sarahdufour06@gmail.com</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -8453,17 +8453,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>charles</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Newman</t>
+          <t>dufour</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>bennboss18@gmail.com</t>
+          <t>charlesdufour04@gmail.com</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -8475,17 +8475,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Gould</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>henryjpickett@hotmail.com</t>
+          <t>rebeccajoegould@gmail.com</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -8497,17 +8497,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Cedar</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Reisman</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>cedarreisman@gmail.com</t>
+          <t>red_14santos@yahoo.com</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -8519,17 +8519,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>truaisch</t>
+          <t>Newman</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>jptruaisch@gmail.com</t>
+          <t>bennboss18@gmail.com</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -8541,17 +8541,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>noah.brown42@icloud.com</t>
+          <t>henryjpickett@hotmail.com</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -8563,17 +8563,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Cedar</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Reisman</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>patrickdpickett@gmail.com</t>
+          <t>cedarreisman@gmail.com</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Samis</t>
+          <t>truaisch</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>michaelsamis18@gmail.com</t>
+          <t>jptruaisch@gmail.com</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -8607,17 +8607,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>thomas_hanna77@hotmail.com</t>
+          <t>noah.brown42@icloud.com</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -8629,17 +8629,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Gurbir</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Osahan</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>osahang@gmail.com</t>
+          <t>patrickdpickett@gmail.com</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -8651,17 +8651,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Samis</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>pickett.thomas@gmail.com</t>
+          <t>michaelsamis18@gmail.com</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Matias</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Veiga</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>matias.veiga24@gmail.com</t>
+          <t>thomas_hanna77@hotmail.com</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -8695,17 +8695,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Gurbir</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Osahan</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>mccaughen@hotmail.com</t>
+          <t>osahang@gmail.com</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Boadway</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>thomasboadway2012@gmail.com</t>
+          <t>pickett.thomas@gmail.com</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -8739,17 +8739,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Sydona</t>
+          <t>Matias</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Veiga</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>sydona.elliott55@gmail.com</t>
+          <t>matias.veiga24@gmail.com</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -8761,17 +8761,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>meech</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>taylor_meech@outlook.com</t>
+          <t>mccaughen@hotmail.com</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -8783,17 +8783,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Kylee</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Suraci</t>
+          <t>Boadway</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>kyleekylend@gmail.com</t>
+          <t>thomasboadway2012@gmail.com</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -8805,17 +8805,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>kostin</t>
+          <t>Sydona</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>blakely</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>shawnchambers20221@gmail.com</t>
+          <t>sydona.elliott55@gmail.com</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -8827,17 +8827,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Lachlann</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Bremner</t>
+          <t>meech</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>lachlanbremner@gmail.com</t>
+          <t>taylor_meech@outlook.com</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -8849,17 +8849,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Kylee</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Cennelly</t>
+          <t>Suraci</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>cennelly.weld@gmail.com</t>
+          <t>kyleekylend@gmail.com</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -8871,17 +8871,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ellie</t>
+          <t>kostin</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>blakely</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>elliew8896@gmail.com</t>
+          <t>shawnchambers20221@gmail.com</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -8893,17 +8893,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>hong</t>
+          <t>Lachlann</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Bremner</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>hongli8017@hotmail.com</t>
+          <t>lachlanbremner@gmail.com</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -8915,17 +8915,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Manley</t>
+          <t>Cennelly</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>manleyjack628@gmail.com</t>
+          <t>cennelly.weld@gmail.com</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -8937,17 +8937,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Thorin</t>
+          <t>ellie</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>bremner</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>nmcdougall16@gmail.com</t>
+          <t>elliew8896@gmail.com</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -8959,17 +8959,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>montie</t>
+          <t>hong</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>foxwell</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>montie@ibeam.ca</t>
+          <t>hongli8017@hotmail.com</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -8981,20 +8981,328 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Manley</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>manleyjack628@gmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Thorin</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>bremner</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>nmcdougall16@gmail.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>montie</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>foxwell</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>montie@ibeam.ca</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
           <t>Deke</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>Osterhout</t>
         </is>
       </c>
-      <c r="C440" t="inlineStr">
+      <c r="C443" t="inlineStr">
         <is>
           <t>dekeo1507@gmail.com</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Rikley</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>damian.rikley@gmail.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Kimberly</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Bremner</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>mskimberleyb@gmail.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Meher</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Kazmi</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>meherkazmi@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Caracciolo</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>isabellarob@icloud.com</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Zegouras</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>albrt278@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Nancy</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Osbourne</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>nanjer@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Natalie</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>natalieknecht@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Xu</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>justin.e.xu@icloud.com</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Damian</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Caracciolo</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>damiancaracciolo24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>tylercord2009@icloud.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Lyla</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Kennelly</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>kennelly@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Belleville.xlsx
+++ b/docs/downloads/Belleville.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D454"/>
+  <dimension ref="A1:D487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daphne</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chang</t>
+          <t>Wachner</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hwah0902@gmail.com</t>
+          <t>awachnerextra@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wachner</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>awachnerextra@gmail.com</t>
+          <t>kevintaylor506@hotmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Russell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kevintaylor506@hotmail.com</t>
+          <t>johnkrussell10@gmail.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kory</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Russell</t>
+          <t>Moxam</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>johnkrussell10@gmail.com</t>
+          <t>korymoxam11299@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kory</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Moxam</t>
+          <t>De jeuses-gautier</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>korymoxam11299@gmail.com</t>
+          <t>kathleendejeuses@yahoo.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Beth</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>De jeuses-gautier</t>
+          <t>Kukkonen</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kathleendejeuses@yahoo.com</t>
+          <t>beth.kukkonen@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Beth</t>
+          <t>Ken</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kukkonen</t>
+          <t>Alwell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>beth.kukkonen@gmail.com</t>
+          <t>ken.alwell50@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ken</t>
+          <t>Adele</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alwell</t>
+          <t>Tate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ken.alwell50@gmail.com</t>
+          <t>ruby.adele.tate@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adele</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tate</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ruby.adele.tate@gmail.com</t>
+          <t>gk@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Barbeau</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>gk@gmail.com</t>
+          <t>jimbarbeau8@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Kalvin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Barbeau</t>
+          <t>Holland</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jimbarbeau8@gmail.com</t>
+          <t>kalvin.holland4@gmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kalvin</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Holland</t>
+          <t>Kapadiya</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kalvin.holland4@gmail.com</t>
+          <t>rktemp@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kapadiya</t>
+          <t>De jong</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rktemp@gmail.com</t>
+          <t>jjdejong14@outlook.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Markus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>De jong</t>
+          <t>Morin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jjdejong14@outlook.com</t>
+          <t>markus.p.morin@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Markus</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Morin</t>
+          <t>Hill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>markus.p.morin@gmail.com</t>
+          <t>kerryhill65@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Donald</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hill</t>
+          <t>Montgomery</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kerryhill65@gmail.com</t>
+          <t>donlinda2002@hotmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donald</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Montgomery</t>
+          <t>Kerr</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>donlinda2002@hotmail.com</t>
+          <t>kerrwood@gmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Jane</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kerrwood@gmail.com</t>
+          <t>abcdef$$@icloud.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jane</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Lipan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abcdef$$@icloud.com</t>
+          <t>rlipan@hotmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Miya</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lipan</t>
+          <t>Hemmersbach</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rlipan@hotmail.com</t>
+          <t>miya.hemmersbach@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Miya</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hemmersbach</t>
+          <t>Reyburn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>miya.hemmersbach@gmail.com</t>
+          <t>jim@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Reyburn</t>
+          <t>Boyce</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jim@pickleplexclub.ca</t>
+          <t>angela.trick@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Boyce</t>
+          <t>Moreton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>angela.trick@gmail.com</t>
+          <t>dropmeoff@hotmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moreton</t>
+          <t>Tai</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>dropmeoff@hotmail.com</t>
+          <t>comtk0@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tai</t>
+          <t>Gk</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>comtk0@gmail.com</t>
+          <t>hggiguig@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>Teresa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gk</t>
+          <t>O'neil</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hggiguig@gmail.com</t>
+          <t>doneil17@cogeco.ca</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Teresa</t>
+          <t>Ruth</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>O'neil</t>
+          <t>Mckinnon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>doneil17@cogeco.ca</t>
+          <t>ruth.m@safestart.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ruth</t>
+          <t>Alistair</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mckinnon</t>
+          <t>Widling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ruth.m@safestart.com</t>
+          <t>dorianwidling@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alistair</t>
+          <t>Cathy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Widling</t>
+          <t>Warren</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>dorianwidling@gmail.com</t>
+          <t>catherineswarren@gmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cathy</t>
+          <t>Khushi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Warren</t>
+          <t>Prajapati</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>catherineswarren@gmail.com</t>
+          <t>kptest@gmail.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Khushi</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Prajapati</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kptest@gmail.com</t>
+          <t>rileydavidson23@icloud.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rileydavidson23@icloud.com</t>
+          <t>timschaly58@gmail.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,17 +1425,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Ludington</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>timschaly58@gmail.com</t>
+          <t>jacobludington@icloud.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1447,17 +1447,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ludington</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jacobludington@icloud.com</t>
+          <t>belleville@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1469,17 +1469,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>belleville@pickleplexclub.ca</t>
+          <t>austinschaly1@gmail.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1491,17 +1491,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Mayhew</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>austinschaly1@gmail.com</t>
+          <t>steven62mayhew@gmail.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1513,17 +1513,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mayhew</t>
+          <t>Delong</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>steven62mayhew@gmail.com</t>
+          <t>delongla36@gmail.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1535,17 +1535,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Delong</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>delongla36@gmail.com</t>
+          <t>mzjonesey@gmail.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1557,17 +1557,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Kukkonen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>mzjonesey@gmail.com</t>
+          <t>dave.kukkonen@gmail.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1579,17 +1579,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Deanna</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kukkonen</t>
+          <t>Sundberg</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>dave.kukkonen@gmail.com</t>
+          <t>deanna@teamfussyhussey.ca</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1601,17 +1601,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Deanna</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sundberg</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>deanna@teamfussyhussey.ca</t>
+          <t>ajones19@hotmail.ca</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1623,17 +1623,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Robby</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Ramos</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ajones19@hotmail.ca</t>
+          <t>robbymachadoramos@gmail.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1645,17 +1645,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Robby</t>
+          <t>Stacy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ramos</t>
+          <t>Merriam</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>robbymachadoramos@gmail.com</t>
+          <t>smerriam44@icloud.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,17 +1667,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Stacy</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Merriam</t>
+          <t>Schaly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>smerriam44@icloud.com</t>
+          <t>noahschaly@gmail.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1689,17 +1689,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Harry</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Schaly</t>
+          <t>Pittman</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>noahschaly@gmail.com</t>
+          <t>harrythesteelstudman@gmail.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1711,17 +1711,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Harry</t>
+          <t>Sandra</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pittman</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>harrythesteelstudman@gmail.com</t>
+          <t>sdclark1956@gmail.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1733,17 +1733,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sandra</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Hutchinson</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sdclark1956@gmail.com</t>
+          <t>amy.h@safestart.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,17 +1755,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hutchinson</t>
+          <t>Lesage</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>amy.h@safestart.com</t>
+          <t>pmlesage@gmail.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1777,17 +1777,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Leonard</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lesage</t>
+          <t>Bangco</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>pmlesage@gmail.com</t>
+          <t>leonardbangco@gmail.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1799,17 +1799,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Leonard</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bangco</t>
+          <t>Widling</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>leonardbangco@gmail.com</t>
+          <t>karenwidling@gmail.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Widling</t>
+          <t>Isbester</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>karenwidling@gmail.com</t>
+          <t>michelle@orkneyresidential.ca</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1843,17 +1843,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Nigel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Isbester</t>
+          <t>Baigent</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>michelle@orkneyresidential.ca</t>
+          <t>nigel@canadianwindowcompany.ca</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -1865,17 +1865,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nigel</t>
+          <t>Lachlan</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Baigent</t>
+          <t>Conlon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nigel@canadianwindowcompany.ca</t>
+          <t>conlon.lachlan@gmail.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1887,17 +1887,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lachlan</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Conlon</t>
+          <t>Humber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>conlon.lachlan@gmail.com</t>
+          <t>andrealouise@icloud.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1909,17 +1909,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Humber</t>
+          <t>Cimprich</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>andrealouise@icloud.com</t>
+          <t>ritasretreat@outlook.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -1931,17 +1931,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cimprich</t>
+          <t>Hydamen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ritasretreat@outlook.com</t>
+          <t>abcdef&amp;&amp;@icloud.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Kaelan</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hydamen</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abcdef&amp;&amp;@icloud.com</t>
+          <t>kaelanfraser@gmail.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -1975,17 +1975,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kaelan</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Davidson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>kaelanfraser@gmail.com</t>
+          <t>davidsonconnor40@gmail.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -1997,17 +1997,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>Teves</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>davidsonconnor40@gmail.com</t>
+          <t>steveteves@hotmail.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Teves</t>
+          <t>Bowman</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>steveteves@hotmail.com</t>
+          <t>nickbowman2009@hotmail.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2041,17 +2041,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nick</t>
+          <t>Botts</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bowman</t>
+          <t>Botterill</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>nickbowman2009@hotmail.com</t>
+          <t>botts@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2063,17 +2063,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Botts</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Botterill</t>
+          <t>Townsend</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>botts@pickleplexclub.ca</t>
+          <t>anntownsend@outlook.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2085,19 +2085,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ann</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Townsend</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>anntownsend@outlook.com</t>
-        </is>
-      </c>
+          <t>Cadavid</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2107,15 +2103,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Elizabeth</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cadavid</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Lorenzoni</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>liz.a.lorenzoni@gmail.com</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2125,19 +2125,15 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Elizabeth</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lorenzoni</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>liz.a.lorenzoni@gmail.com</t>
-        </is>
-      </c>
+          <t>Fulton</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -2147,12 +2143,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Brielle</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fulton</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2165,12 +2161,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Brielle</t>
+          <t>Ivy</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Walton</t>
+          <t>O'Coin</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2183,7 +2179,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ivy</t>
+          <t>Kristen</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2201,7 +2197,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kristen</t>
+          <t>Ember</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2219,7 +2215,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ember</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2237,12 +2233,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Zara</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O'Coin</t>
+          <t>Caletti</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2255,12 +2251,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Zara</t>
+          <t>Rudra</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Caletti</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2273,12 +2269,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rudra</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2291,12 +2287,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2309,12 +2305,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Mya</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2327,12 +2323,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mya</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2345,12 +2341,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Brettley</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Surerus</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2363,12 +2359,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Brettley</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Surerus</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2381,12 +2377,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Rylan</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2399,12 +2395,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Rylan</t>
+          <t>ALYSSA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2417,12 +2413,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ALYSSA</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2435,12 +2431,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2453,12 +2449,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Williams</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2471,12 +2467,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Williams</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2489,12 +2485,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2507,12 +2503,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Barrett</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>LaPalm</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2525,12 +2521,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Barrett</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LaPalm</t>
+          <t>McNulty</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2543,12 +2539,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>McNulty</t>
+          <t>Goldsmith</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2561,12 +2557,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Haylen</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Goldsmith</t>
+          <t>Foote</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2579,12 +2575,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Haylen</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foote</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2597,12 +2593,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Bethany</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2615,12 +2611,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bethany</t>
+          <t>Misty</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2633,12 +2629,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Misty</t>
+          <t>Emmett</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Mamajek</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2651,12 +2647,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Emmett</t>
+          <t>Dinah</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Mamajek</t>
+          <t>Ramin</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2669,12 +2665,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Dinah</t>
+          <t>Lyla</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ramin</t>
+          <t>Richter</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2687,12 +2683,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Lyla</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Richter</t>
+          <t>Tipper</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2705,12 +2701,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tipper</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2723,12 +2719,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2741,12 +2737,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Coulter</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2759,12 +2755,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Coulter</t>
+          <t>Hart</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2777,12 +2773,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Moira</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Hart</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2795,12 +2791,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Moira</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2813,12 +2809,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2831,12 +2827,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Latchford</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2849,12 +2845,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Latchford</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2867,12 +2863,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2885,12 +2881,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2903,12 +2899,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Juliet</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Zhu</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2921,12 +2917,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Juliet</t>
+          <t>Farah</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Zhu</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2939,7 +2935,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Farah</t>
+          <t>Jameel</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2957,12 +2953,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Jameel</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Pendleton</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2975,12 +2971,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Pendleton</t>
+          <t>Fournier</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2993,12 +2989,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Fournier</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3011,12 +3007,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Neeson</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3029,12 +3025,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Neeson</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Cyril</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3047,12 +3043,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Kade</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cyril</t>
+          <t>Vestervelt</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3065,12 +3061,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Vestervelt</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3083,12 +3079,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>Bassett-Spiers</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3101,12 +3097,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Sunny</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bassett-Spiers</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3119,12 +3115,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sunny</t>
+          <t>Keith</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Roberton</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3137,12 +3133,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Keith</t>
+          <t>nathan</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Roberton</t>
+          <t>Shillington</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3155,12 +3151,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>nathan</t>
+          <t>Blythe</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shillington</t>
+          <t>Crowley</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3173,12 +3169,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Blythe</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Crowley</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3191,12 +3187,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>greg</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Papakiriazis</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3209,12 +3205,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>greg</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Papakiriazis</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3227,12 +3223,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Marley</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Philp</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3245,12 +3241,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Marley</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Philp</t>
+          <t>Penney</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3263,12 +3259,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Penney</t>
+          <t>Bentley</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3281,12 +3277,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jadyn</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>Brouillard</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3299,12 +3295,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Jadyn</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Brouillard</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3317,12 +3313,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Vreugdenhil</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3335,12 +3331,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vreugdenhil</t>
+          <t>Rittwage</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3353,12 +3349,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Rittwage</t>
+          <t>Domiguiano</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3371,12 +3367,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Chase</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Domiguiano</t>
+          <t>Robinson</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3389,12 +3385,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Chase</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Robinson</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3407,12 +3403,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Yasmeen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Kaukab</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3425,12 +3421,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Yasmeen</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Kaukab</t>
+          <t>Hall</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3443,12 +3439,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hall</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3461,12 +3457,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Rhys</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3479,12 +3475,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Rhys</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Di Sandolo</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3497,12 +3493,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Killian</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Di Sandolo</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3515,12 +3511,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Killian</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Tetlock</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3533,12 +3529,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tetlock</t>
+          <t>Fargey</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3551,12 +3547,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fargey</t>
+          <t>Dominguiano</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3569,12 +3565,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Addesyn</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Dominguiano</t>
+          <t>Ibbotson</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3587,12 +3583,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Addesyn</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ibbotson</t>
+          <t>Gledhill</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3605,12 +3601,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Randy</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Gledhill</t>
+          <t>McCullough</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3623,12 +3619,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Randy</t>
+          <t>Cara</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>McCullough</t>
+          <t>Halligan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3641,12 +3637,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cara</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Halligan</t>
+          <t>Darrah</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3659,12 +3655,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Eve</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Darrah</t>
+          <t>michell</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3677,12 +3673,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Eve</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>michell</t>
+          <t>Burtnik</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3695,12 +3691,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Aliya</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Burtnik</t>
+          <t>Vriesema</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3713,12 +3709,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Aliya</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Vriesema</t>
+          <t>Windover</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3731,12 +3727,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Cormac</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Windover</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3749,12 +3745,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cormac</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Angove</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3767,12 +3763,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sam</t>
+          <t>Joey</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Angove</t>
+          <t>Cretney</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3785,12 +3781,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Joey</t>
+          <t>Erica</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cretney</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3803,12 +3799,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Erica</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Cyr</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3821,12 +3817,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cyr</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3839,12 +3835,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Bonn</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3857,12 +3853,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Bonn</t>
+          <t>Schier</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3875,12 +3871,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Lucy</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Schier</t>
+          <t>Henshaw</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3893,12 +3889,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Henshaw</t>
+          <t>Norris</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3911,12 +3907,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Julius</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Norris</t>
+          <t>Carballo</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3929,12 +3925,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Julius</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Carballo</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3947,12 +3943,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3965,12 +3961,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Simpson</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3983,12 +3979,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Simpson</t>
+          <t>Maracle</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4001,12 +3997,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Maracle</t>
+          <t>Troy</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4019,12 +4015,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Jonas</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Troy</t>
+          <t>Mccoy</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4037,12 +4033,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Jonas</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mccoy</t>
+          <t>morgante</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4055,12 +4051,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>morgante</t>
+          <t>Patry</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4073,12 +4069,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Patry</t>
+          <t>Gleeson</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4091,12 +4087,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Gleeson</t>
+          <t>Grimes</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4109,12 +4105,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Rowen</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Grimes</t>
+          <t>Gleeson</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4127,12 +4123,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Rowen</t>
+          <t>Davianna</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Gleeson</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4145,12 +4141,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Davianna</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Bell</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4163,12 +4159,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Lilly</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bell</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4181,12 +4177,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Lilly</t>
+          <t>hendrik</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4199,12 +4195,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>hendrik</t>
+          <t>Blake</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4217,12 +4213,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Blake</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4235,12 +4231,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Sacha</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>Caritey</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4253,12 +4249,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sacha</t>
+          <t>Wallis</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Caritey</t>
+          <t>Irvine</t>
         </is>
       </c>
       <c r="C196" t="inlineStr"/>
@@ -4271,12 +4267,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Wallis</t>
+          <t>Kayla</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Irvine</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4289,12 +4285,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kayla</t>
+          <t>isaac</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>bruinsma</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4307,12 +4303,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>isaac</t>
+          <t>BHAVIK</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>bruinsma</t>
+          <t>PATEL</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4325,12 +4321,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>BHAVIK</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PATEL</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4343,12 +4339,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>will</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4361,12 +4357,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>will</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Pixley</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4379,12 +4375,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Jamieson</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Pixley</t>
+          <t>Hunter</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4397,12 +4393,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Jamieson</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Hunter</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4415,12 +4411,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Tyler</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Calvert-Challice</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4433,12 +4429,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Calvert-Challice</t>
+          <t>Masotti</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4451,12 +4447,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Masotti</t>
+          <t>Calvert</t>
         </is>
       </c>
       <c r="C207" t="inlineStr"/>
@@ -4469,12 +4465,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Alkina</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Calvert</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4487,15 +4483,19 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Alkina</t>
+          <t>Janet</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Feng</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr"/>
+          <t>Riley</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>janetrileybowen@gmail.com</t>
+        </is>
+      </c>
       <c r="D209" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4505,19 +4505,15 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Janet</t>
+          <t>Luke</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Riley</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>janetrileybowen@gmail.com</t>
-        </is>
-      </c>
+          <t>Dunn</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -4527,12 +4523,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Luke</t>
+          <t>vada</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>martin</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4545,12 +4541,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>vada</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>martin</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4563,12 +4559,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Sophia</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Fajardo</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4581,12 +4577,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Fajardo</t>
+          <t>Zuwerkalow</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4599,12 +4595,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Zuwerkalow</t>
+          <t>Dunn</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4617,12 +4613,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Brett</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Dunn</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4635,12 +4631,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Brett</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Harris</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4653,12 +4649,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>Kelly-Clarke</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4671,12 +4667,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Kelly-Clarke</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4689,12 +4685,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Tessa</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4707,12 +4703,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Tessa</t>
+          <t>Jessy</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4725,12 +4721,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Jessy</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Sokaywatt</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4743,12 +4739,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Kole</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Sokaywatt</t>
+          <t>Krueger</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4761,12 +4757,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Kole</t>
+          <t>Carley-Jo</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Krueger</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4779,12 +4775,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Carley-Jo</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4797,12 +4793,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Xiaoyi</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4815,12 +4811,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Xiaoyi</t>
+          <t>Lyndsay</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4833,12 +4829,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Lyndsay</t>
+          <t>Abraham</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4851,12 +4847,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Abraham</t>
+          <t>Siraj</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4869,12 +4865,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Siraj</t>
+          <t>Maddox</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4887,12 +4883,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Maddox</t>
+          <t>Theodore</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Munday</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4905,12 +4901,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Theodore</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Munday</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4923,12 +4919,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Gabriel</t>
+          <t>Nico</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>DiPietrantonio</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -4941,12 +4937,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Nico</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DiPietrantonio</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4959,12 +4955,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Devin</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>Cousins</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -4977,12 +4973,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Devin</t>
+          <t>Faris</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Cousins</t>
+          <t>Abdul Rahman</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -4995,12 +4991,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Faris</t>
+          <t>Trent</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Abdul Rahman</t>
+          <t>Clow</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5013,12 +5009,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Trent</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Clow</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5031,12 +5027,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Lupili</t>
+          <t>Christiansen</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5049,12 +5045,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Christiansen</t>
+          <t>Tripp</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5067,12 +5063,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Elora</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Tripp</t>
+          <t>Yates</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5085,12 +5081,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Elora</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Yates</t>
+          <t>laurin</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5103,12 +5099,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>laurin</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5121,12 +5117,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5139,12 +5135,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Rosalind</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Walton</t>
+          <t>Mulligan-Anderson</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5157,12 +5153,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Rosalind</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Mulligan-Anderson</t>
+          <t>Smolders</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5175,12 +5171,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Alyssa</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Smolders</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5193,12 +5189,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Alyssa</t>
+          <t>Beccah</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Le Marchant</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5211,12 +5207,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Beccah</t>
+          <t>Xi</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Le Marchant</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5229,12 +5225,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Xi</t>
+          <t>Audrey-Mae</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5247,12 +5243,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Audrey-Mae</t>
+          <t>Levi</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Mallory</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5265,12 +5261,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Levi</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Mallory</t>
+          <t>Munroe</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5283,12 +5279,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Munroe</t>
+          <t>Corning</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5301,12 +5297,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Corning</t>
+          <t>Holbrough</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5319,12 +5315,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Kaiden</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Holbrough</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5337,12 +5333,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Kaiden</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Bucknell</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5355,12 +5351,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Bucknell</t>
+          <t>Bonacci</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5373,12 +5369,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Callie</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Bonacci</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5391,12 +5387,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Callie</t>
+          <t>Charlee</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Quinn-Black</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5409,12 +5405,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Charlee</t>
+          <t>Madi</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Quinn-Black</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5427,12 +5423,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Madi</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Pettey</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5445,12 +5441,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Pettey</t>
+          <t>Thompson</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5463,12 +5459,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Thompson</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5481,12 +5477,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Penn</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Poskin</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5499,12 +5495,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Poskin</t>
+          <t>Moore</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5517,12 +5513,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Ewan</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Moore</t>
+          <t>Dahle</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5535,12 +5531,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Ewan</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Dahle</t>
+          <t>Larmer</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5553,12 +5549,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Larmer</t>
+          <t>Wilkinson</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5571,12 +5567,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Isaiah</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Wilkinson</t>
+          <t>Lupili</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5589,15 +5585,19 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Isaiah</t>
+          <t>Lindon</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Lupili</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>Zhuo</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>lindonzhuo@gmail.com</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -5607,17 +5607,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Lindon</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Zhuo</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>lindonzhuo@gmail.com</t>
+          <t>cnthbeach@gmail.com</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6421,17 +6421,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>fahad</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Vaid</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>varun@ttkrealestateteam.com</t>
+          <t>fahad.ecsp@gmail.com</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6591,17 +6591,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>kiyan</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>mahmood</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>dkrawczyk@belleville.ca</t>
+          <t>kiyan.mahmood07@gmail.com</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -6613,15 +6613,19 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Kai</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Newar</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr"/>
+          <t>Krawczyk</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>dkrawczyk@belleville.ca</t>
+        </is>
+      </c>
       <c r="D324" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6631,19 +6635,15 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Suzanne</t>
+          <t>Kai</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Maracle</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>70spoldon@quintehealth.ca</t>
-        </is>
-      </c>
+          <t>Newar</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6653,15 +6653,19 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Easton</t>
+          <t>Suzanne</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Macdonald</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr"/>
+          <t>Maracle</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>70spoldon@quintehealth.ca</t>
+        </is>
+      </c>
       <c r="D326" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6671,12 +6675,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Finley</t>
+          <t>Easton</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6689,7 +6693,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Finley</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -6707,19 +6711,15 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Joanne</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Klemencic</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>jk.klemencic@gmail.com</t>
-        </is>
-      </c>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6729,17 +6729,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Donna</t>
+          <t>Joanne</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Klemencic</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>duncand@hastingscounty.com</t>
+          <t>jk.klemencic@gmail.com</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -6751,17 +6751,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Donna</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Esau</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>sesau@belleville.ca</t>
+          <t>duncand@hastingscounty.com</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -6773,17 +6773,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Esau</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>cindy.w@safestart.com</t>
+          <t>sesau@belleville.ca</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -6795,89 +6795,89 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
+          <t>Cindy</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>cindy.w@safestart.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
           <t>Theresa</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>Green</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
+      <c r="C334" t="inlineStr">
         <is>
           <t>tgreen@hpedsb.on.ca</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr"/>
-      <c r="B334" t="inlineStr"/>
-      <c r="C334" t="inlineStr">
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr"/>
+      <c r="B335" t="inlineStr"/>
+      <c r="C335" t="inlineStr">
         <is>
           <t>tomg@bel-con.com</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>Julie</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>Muli</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
+      <c r="C336" t="inlineStr">
         <is>
           <t>jmuli@cmhs-hpe.on.ca</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr"/>
-      <c r="B336" t="inlineStr"/>
-      <c r="C336" t="inlineStr">
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr"/>
+      <c r="B337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
         <is>
           <t>barryk@otgroup.ca</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Avery</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Gretzky</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>agretzky@petersmithgm.com</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -6889,17 +6889,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Parker</t>
+          <t>Gretzky</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>tedp@youthab.ca</t>
+          <t>agretzky@petersmithgm.com</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -6911,15 +6911,19 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>daphne</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>quick</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
+          <t>Parker</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>tedp@youthab.ca</t>
+        </is>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6929,7 +6933,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>bradley</t>
+          <t>daphne</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -6947,19 +6951,15 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Sharon</t>
+          <t>bradley</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Adams</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>rbough@qhc.on.ca</t>
-        </is>
-      </c>
+          <t>quick</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -6969,17 +6969,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Sharon</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Garrard</t>
+          <t>Adams</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>michelle.garrard@bardonsupplies.com</t>
+          <t>rbough@qhc.on.ca</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -6991,17 +6991,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>Garrard</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>bgrant@trianglefluid.com</t>
+          <t>michelle.garrard@bardonsupplies.com</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7013,17 +7013,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Bradley</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Marchand</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>smarchand@maxwellpaper.ca</t>
+          <t>bgrant@trianglefluid.com</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7035,53 +7035,53 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Marchand</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>smarchand@maxwellpaper.ca</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>Seward</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
+      <c r="C346" t="inlineStr">
         <is>
           <t>rseward@reidsdairy.com</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr"/>
-      <c r="B346" t="inlineStr"/>
-      <c r="C346" t="inlineStr">
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr"/>
+      <c r="B347" t="inlineStr"/>
+      <c r="C347" t="inlineStr">
         <is>
           <t>maryanne.wooldridge@ceo.ymca.ca</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Madison</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>mwhite@clbelleville.ca</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7093,53 +7093,53 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
+          <t>Madison</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>mwhite@clbelleville.ca</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
           <t>Crystal</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>Johnston</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
+      <c r="C349" t="inlineStr">
         <is>
           <t>crystal.johnston@ems-tech.net</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr"/>
-      <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr">
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr"/>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr">
         <is>
           <t>eric@impacto.ca</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Amber</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>Leonard-Free</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>aleonard-free@bellevilleps.ca</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7151,17 +7151,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Alissa</t>
+          <t>Amber</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Partington</t>
+          <t>Leonard-Free</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>apartington@cmhahpe.ca</t>
+          <t>aleonard-free@bellevilleps.ca</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7173,67 +7173,75 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
+          <t>Alissa</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Partington</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>apartington@cmhahpe.ca</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
           <t>Landan</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>Burns-Keaney</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
+      <c r="C353" t="inlineStr">
         <is>
           <t>landanb@pathwaysind.com</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr"/>
-      <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr">
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr"/>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr">
         <is>
           <t>aide@mix97.com</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>Juliana</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>Finney</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
+      <c r="C355" t="inlineStr">
         <is>
           <t>finneyj@hastingscounty.com</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr"/>
-      <c r="B355" t="inlineStr"/>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>loris.clarke@whitleynewman.com</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7247,41 +7255,41 @@
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="inlineStr">
         <is>
+          <t>loris.clarke@whitleynewman.com</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr"/>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
           <t>mmacdonald@jewelleng.ca</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>James</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>Clack</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr"/>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr"/>
-      <c r="B358" t="inlineStr"/>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>thompsonellisk@bellevillesens.com</t>
-        </is>
-      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7293,29 +7301,21 @@
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr">
         <is>
+          <t>thompsonellisk@bellevillesens.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr"/>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr">
+        <is>
           <t>nbowland@bcsautomation.ca</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Sowmia</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>Chalissery</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>schalissery@beclawat.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7327,53 +7327,53 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
+          <t>Sowmia</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Chalissery</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>schalissery@beclawat.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
           <t>Barb</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>Cook</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
+      <c r="C362" t="inlineStr">
         <is>
           <t>barbcook@royallepage.ca</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr"/>
-      <c r="B362" t="inlineStr"/>
-      <c r="C362" t="inlineStr">
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr"/>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr">
         <is>
           <t>acooney@cooney.ca</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Jennifer</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>Marvin</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>marvinj@bqwchc.com</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7385,17 +7385,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Gillis</t>
+          <t>Marvin</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>sgillis@mcdougallinsurance.com</t>
+          <t>marvinj@bqwchc.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7407,17 +7407,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Travis</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Kupar</t>
+          <t>Gillis</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>travis@truckright.ca</t>
+          <t>sgillis@mcdougallinsurance.com</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7429,31 +7429,39 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
+          <t>Travis</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Kupar</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>travis@truckright.ca</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
           <t>Stella</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>Haskin</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
+      <c r="C367" t="inlineStr">
         <is>
           <t>shaskin@albertcollege.ca</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr"/>
-      <c r="B367" t="inlineStr"/>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>kcrowe@alarmsys.com</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -7467,29 +7475,21 @@
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="inlineStr">
         <is>
+          <t>kcrowe@alarmsys.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr"/>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
           <t>james.hunt@ucbradio.com</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Radhika</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>radhika@loyalistcollege.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7501,89 +7501,89 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>radhika@loyalistcollege.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>Anthony</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>Kessel</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
+      <c r="C371" t="inlineStr">
         <is>
           <t>christofere@metaservices.ca</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr"/>
-      <c r="B371" t="inlineStr"/>
-      <c r="C371" t="inlineStr">
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr"/>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr">
         <is>
           <t>akeys@emhware.com</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>Lavanna</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>Luong</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C373" t="inlineStr">
         <is>
           <t>lavanna.luong@highlandshorescas.com</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr"/>
-      <c r="B373" t="inlineStr"/>
-      <c r="C373" t="inlineStr">
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr"/>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr">
         <is>
           <t>tim@jaatsolutions.com</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>belleville@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Cherie</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>Horschman</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>cherie.horschman@heliahealthcare.com</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -7595,15 +7595,19 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Cherie</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Picard</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr"/>
+          <t>Horschman</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>cherie.horschman@heliahealthcare.com</t>
+        </is>
+      </c>
       <c r="D375" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7613,7 +7617,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Ellie</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -7631,12 +7635,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Ellie</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>zanette</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -7649,12 +7653,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Picard</t>
+          <t>zanette</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -7667,12 +7671,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>owen</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>lindsay</t>
+          <t>Picard</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -7685,12 +7689,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>owen</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Picard</t>
+          <t>lindsay</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -7703,19 +7707,15 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>TARAH</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>ALEXANDER</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>bellevillebearcatsu18a@gmail.com</t>
-        </is>
-      </c>
+          <t>Picard</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7725,15 +7725,19 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>TARAH</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Ramlochan</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr"/>
+          <t>ALEXANDER</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>bellevillebearcatsu18a@gmail.com</t>
+        </is>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7743,12 +7747,12 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>myron</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>ibrahim</t>
+          <t>Ramlochan</t>
         </is>
       </c>
       <c r="C383" t="inlineStr"/>
@@ -7761,7 +7765,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>mateo</t>
+          <t>myron</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -7779,12 +7783,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>mateo</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Rowe</t>
+          <t>ibrahim</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -7797,7 +7801,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Bohdan</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -7815,19 +7819,15 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Bohdan</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Gregorio</t>
-        </is>
-      </c>
-      <c r="C387" t="inlineStr">
-        <is>
-          <t>maureen.gregorio@gmail.com</t>
-        </is>
-      </c>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
@@ -7837,17 +7837,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Aleesha</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Gregorio</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>siddiqi.aleesha@gmail.com</t>
+          <t>maureen.gregorio@gmail.com</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -7859,17 +7859,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Aleesha</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Haskins</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>shaskins321@gmail.com</t>
+          <t>siddiqi.aleesha@gmail.com</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>emma.haskins@hotmail.com</t>
+          <t>shaskins321@gmail.com</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -7903,17 +7903,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Shackleton</t>
+          <t>Haskins</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>shackleton.at@gmail.com</t>
+          <t>emma.haskins@hotmail.com</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -7925,17 +7925,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Miller</t>
+          <t>Shackleton</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>jordanmillerjune20@gmail.com</t>
+          <t>shackleton.at@gmail.com</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -7947,17 +7947,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>Miller</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>nicolas.dufour@gmail.com</t>
+          <t>jordanmillerjune20@gmail.com</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -7969,17 +7969,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Beverly</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>beverly924@hotmail.com</t>
+          <t>nicolas.dufour@gmail.com</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -7991,17 +7991,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Beverly</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Shackleton</t>
+          <t>Mann</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>shackleton.ac@gmail.com</t>
+          <t>beverly924@hotmail.com</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -8013,17 +8013,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Cull</t>
+          <t>Shackleton</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>cullscott@gmail.com</t>
+          <t>shackleton.ac@gmail.com</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -8035,17 +8035,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Cull</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>agilesamurai7@gmail.com</t>
+          <t>cullscott@gmail.com</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -8057,17 +8057,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Michal</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Rajczewski</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>rajczewskim@gmail.com</t>
+          <t>agilesamurai7@gmail.com</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -8079,17 +8079,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>christine</t>
+          <t>Michal</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>cull</t>
+          <t>Rajczewski</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>christinecull33@gmail.com</t>
+          <t>rajczewskim@gmail.com</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -8101,17 +8101,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Nicole</t>
+          <t>christine</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Lamoureux</t>
+          <t>cull</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ronirejo@gmail.com</t>
+          <t>christinecull33@gmail.com</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -8123,17 +8123,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Aylen</t>
+          <t>Nicole</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Garcia</t>
+          <t>Lamoureux</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>aylengarseeya@gmail.com</t>
+          <t>ronirejo@gmail.com</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -8145,17 +8145,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Bronwyn</t>
+          <t>Aylen</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>McGeachy</t>
+          <t>Garcia</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>bronwynmcgeachy@gmail.com</t>
+          <t>aylengarseeya@gmail.com</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -8167,17 +8167,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Dante</t>
+          <t>Bronwyn</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Palango</t>
+          <t>McGeachy</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>dante.palango@gmail.com</t>
+          <t>bronwynmcgeachy@gmail.com</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -8189,17 +8189,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Dante</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Ramsay</t>
+          <t>Palango</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>campbellmel@hotmail.com</t>
+          <t>dante.palango@gmail.com</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -8211,17 +8211,17 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Ramsay</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>jlp8353@yahoo.com</t>
+          <t>campbellmel@hotmail.com</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -8233,17 +8233,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Chung</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>calebjechung@gmail.com</t>
+          <t>jlp8353@yahoo.com</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -8255,17 +8255,17 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Bennett</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Ramsay</t>
+          <t>Chung</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>melanieramsay7@gmail.com</t>
+          <t>calebjechung@gmail.com</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -8277,17 +8277,17 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Bennett</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>LaPalm</t>
+          <t>Ramsay</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>jasonlapalm@gmail.com</t>
+          <t>melanieramsay7@gmail.com</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -8299,17 +8299,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Eliza</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Capps-Perry</t>
+          <t>LaPalm</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>cmc23@hotmail.com</t>
+          <t>jasonlapalm@gmail.com</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -8321,17 +8321,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Tess</t>
+          <t>Eliza</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Shakell</t>
+          <t>Capps-Perry</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>shakelltess@gmail.com</t>
+          <t>cmc23@hotmail.com</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -8343,17 +8343,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Tess</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Shakell</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>jposty38@gmail.com</t>
+          <t>shakelltess@gmail.com</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -8365,17 +8365,17 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>isabelle</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>chaput</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>isabellechaput1@gmail.com</t>
+          <t>jposty38@gmail.com</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -8387,17 +8387,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Maude</t>
+          <t>isabelle</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Dufour</t>
+          <t>chaput</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>maudedufour07@gmail.com</t>
+          <t>isabellechaput1@gmail.com</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -8409,17 +8409,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>AUSTIN</t>
+          <t>Maude</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>GENEREAUX</t>
+          <t>Dufour</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>kngsfan072007@gmail.com</t>
+          <t>maudedufour07@gmail.com</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -8431,17 +8431,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>sarah</t>
+          <t>AUSTIN</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>dufour</t>
+          <t>GENEREAUX</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>sarahdufour06@gmail.com</t>
+          <t>kngsfan072007@gmail.com</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -8453,7 +8453,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>charles</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>charlesdufour04@gmail.com</t>
+          <t>sarahdufour06@gmail.com</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -8475,17 +8475,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Rebecca</t>
+          <t>charles</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Gould</t>
+          <t>dufour</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>rebeccajoegould@gmail.com</t>
+          <t>charlesdufour04@gmail.com</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -8497,17 +8497,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Aubrey</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Gould</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>red_14santos@yahoo.com</t>
+          <t>rebeccajoegould@gmail.com</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -8519,17 +8519,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Aubrey</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Newman</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>bennboss18@gmail.com</t>
+          <t>red_14santos@yahoo.com</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -8541,17 +8541,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Newman</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>henryjpickett@hotmail.com</t>
+          <t>bennboss18@gmail.com</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -8563,17 +8563,17 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Cedar</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Reisman</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>cedarreisman@gmail.com</t>
+          <t>henryjpickett@hotmail.com</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -8585,17 +8585,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Cedar</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>truaisch</t>
+          <t>Reisman</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>jptruaisch@gmail.com</t>
+          <t>cedarreisman@gmail.com</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -8607,17 +8607,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>truaisch</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>noah.brown42@icloud.com</t>
+          <t>jptruaisch@gmail.com</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -8629,17 +8629,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Patrick</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>patrickdpickett@gmail.com</t>
+          <t>noah.brown42@icloud.com</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -8651,17 +8651,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Patrick</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Samis</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>michaelsamis18@gmail.com</t>
+          <t>patrickdpickett@gmail.com</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Hanna</t>
+          <t>Samis</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>thomas_hanna77@hotmail.com</t>
+          <t>michaelsamis18@gmail.com</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -8695,17 +8695,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Gurbir</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Osahan</t>
+          <t>Hanna</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>osahang@gmail.com</t>
+          <t>thomas_hanna77@hotmail.com</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -8717,17 +8717,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Gurbir</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Osahan</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>pickett.thomas@gmail.com</t>
+          <t>osahang@gmail.com</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -8739,17 +8739,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Matias</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Veiga</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>matias.veiga24@gmail.com</t>
+          <t>pickett.thomas@gmail.com</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -8761,17 +8761,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Matias</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Pickett</t>
+          <t>Veiga</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>mccaughen@hotmail.com</t>
+          <t>matias.veiga24@gmail.com</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -8783,17 +8783,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Boadway</t>
+          <t>Pickett</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>thomasboadway2012@gmail.com</t>
+          <t>mccaughen@hotmail.com</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -8805,17 +8805,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Sydona</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Boadway</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>sydona.elliott55@gmail.com</t>
+          <t>thomasboadway2012@gmail.com</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -8827,17 +8827,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Sydona</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>meech</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>taylor_meech@outlook.com</t>
+          <t>sydona.elliott55@gmail.com</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -8849,17 +8849,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Kylee</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Suraci</t>
+          <t>meech</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>kyleekylend@gmail.com</t>
+          <t>taylor_meech@outlook.com</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -8871,17 +8871,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>kostin</t>
+          <t>Kylee</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>blakely</t>
+          <t>Suraci</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>shawnchambers20221@gmail.com</t>
+          <t>kyleekylend@gmail.com</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -8893,17 +8893,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Lachlann</t>
+          <t>kostin</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Bremner</t>
+          <t>blakely</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>lachlanbremner@gmail.com</t>
+          <t>shawnchambers20221@gmail.com</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -8915,17 +8915,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Lachlann</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Cennelly</t>
+          <t>Bremner</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>cennelly.weld@gmail.com</t>
+          <t>lachlanbremner@gmail.com</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -8937,17 +8937,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ellie</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Cennelly</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>elliew8896@gmail.com</t>
+          <t>cennelly.weld@gmail.com</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -8959,17 +8959,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>hong</t>
+          <t>ellie</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>hongli8017@hotmail.com</t>
+          <t>elliew8896@gmail.com</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -8981,17 +8981,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>hong</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Manley</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>manleyjack628@gmail.com</t>
+          <t>hongli8017@hotmail.com</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -9003,17 +9003,17 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Thorin</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>bremner</t>
+          <t>Manley</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>nmcdougall16@gmail.com</t>
+          <t>manleyjack628@gmail.com</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -9025,17 +9025,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>montie</t>
+          <t>Thorin</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>foxwell</t>
+          <t>bremner</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>montie@ibeam.ca</t>
+          <t>nmcdougall16@gmail.com</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -9047,17 +9047,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Deke</t>
+          <t>montie</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Osterhout</t>
+          <t>foxwell</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>dekeo1507@gmail.com</t>
+          <t>montie@ibeam.ca</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -9069,17 +9069,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Deke</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Rikley</t>
+          <t>Osterhout</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>damian.rikley@gmail.com</t>
+          <t>dekeo1507@gmail.com</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -9091,17 +9091,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Bremner</t>
+          <t>Rikley</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>mskimberleyb@gmail.com</t>
+          <t>damian.rikley@gmail.com</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -9113,17 +9113,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Meher</t>
+          <t>Kimberly</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Kazmi</t>
+          <t>Bremner</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>meherkazmi@hotmail.com</t>
+          <t>mskimberleyb@gmail.com</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -9135,17 +9135,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Meher</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Caracciolo</t>
+          <t>Kazmi</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>isabellarob@icloud.com</t>
+          <t>meherkazmi@hotmail.com</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -9157,17 +9157,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Zegouras</t>
+          <t>Caracciolo</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>albrt278@hotmail.com</t>
+          <t>isabellarob@icloud.com</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -9179,17 +9179,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Osbourne</t>
+          <t>Zegouras</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>nanjer@hotmail.com</t>
+          <t>albrt278@hotmail.com</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -9201,17 +9201,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Osbourne</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>natalieknecht@hotmail.com</t>
+          <t>nanjer@hotmail.com</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -9223,17 +9223,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Cordeiro</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>justin.e.xu@icloud.com</t>
+          <t>natalieknecht@hotmail.com</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -9245,17 +9245,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Damian</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Caracciolo</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>damiancaracciolo24@gmail.com</t>
+          <t>justin.e.xu@icloud.com</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -9267,17 +9267,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Tyler</t>
+          <t>Damian</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Cordeiro</t>
+          <t>Caracciolo</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>tylercord2009@icloud.com</t>
+          <t>damiancaracciolo24@gmail.com</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -9289,20 +9289,742 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
+          <t>Tyler</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Cordeiro</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>tylercord2009@icloud.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
           <t>Lyla</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>Kennelly</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C455" t="inlineStr">
         <is>
           <t>kennelly@yahoo.com</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Jared</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Langdon</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>jaredmatthew12345@gmail.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Spencer</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>carlosmherreraag@gmail.com</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Beylerian</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>davidbeylerian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Thom</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Spencer</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>carlos@subtlemind.ca</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>McFaul</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>jacobmcfaul7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Canning</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>liamcanning2010@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Derek</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Bresee</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>mbresee@kos.net</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Lisa</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Peters</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>lpeters2009@live.com</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Margaret</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Meban</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>margaret.maban@me.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Bresee</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>mrsbresee@kos.net</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Gary</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Peck</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>garypeck159@gmail.com</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Kaylee</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Vardy</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>kayleevardy@icloud.com</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Walker</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>austinwwalker10@gmail.com</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Rick</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Bouder</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>richardbouder@gmail.com</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Melissa</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Dyche</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>m.dyche@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Hardik</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>hpatel070390@gmail.com</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Hana</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Jovanovic</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>hanajovanovic014@gmail.com</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Kaustubh</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Gandhalikar</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>kgandhalikar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>azhar</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>jinnah</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>azharjinnah@gmail.com</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Jovanovic</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>mayajojo1000@gmail.com</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Laila</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Bouali</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>lailabouali1@gmail.com</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>alexandersharpe9256@gmail.com</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Shea</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Hilts</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>sheahilts14108@gmail.com</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>james</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>huff</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>thevanhuffs@gmail.com</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>josh</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>henderson</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>josh_henderson_92@hotmaill.com</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>SANJYOT</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>HARSHE</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>sanjyotharshe22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>peacock</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>mpeacock975@gmail.com</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>annie</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>houle</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>annie.houle.9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Noreen</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>fnoreen7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>VINUTHA</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>SHENOY</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>vinutha089@gmail.com</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>richard</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>houle</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>tofu_heart1972@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>belleville@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>maverick</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>houle</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
         <is>
           <t>belleville@pickleplex.ca</t>
         </is>
